--- a/database.xlsx
+++ b/database.xlsx
@@ -1,19 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\Semester 7\Laporan\KP - Rival\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C175351-0423-4D9E-A7E6-1385821076EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Database" sheetId="1" r:id="rId4"/>
+    <sheet name="Database" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Database!$A$1:$E$380</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Database!$A$1:$F$381</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="859">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1906" uniqueCount="866">
   <si>
     <t>Asset - Asset#</t>
   </si>
@@ -2590,26 +2600,46 @@
   </si>
   <si>
     <t>NXGCPSN0056421DE6D7600</t>
+  </si>
+  <si>
+    <t>Acer Aspire E5-477</t>
+  </si>
+  <si>
+    <t>PTAII/ASET2021/19</t>
+  </si>
+  <si>
+    <t>NXGCPSN0056421DE6D7700</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Idle</t>
+  </si>
+  <si>
+    <t>Used</t>
+  </si>
+  <si>
+    <t>Error</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
-      <color/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -2618,46 +2648,55 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -2855,21 +2894,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln cap="flat" cmpd="sng" w="12700" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln cap="flat" cmpd="sng" w="19050" algn="ctr">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln cap="flat" cmpd="sng" w="25400" algn="ctr">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -2886,7 +2925,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" rotWithShape="0" algn="ctr" dir="5400000" dist="19050">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -2956,28 +2995,25 @@
     </a:lnDef>
   </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}"/>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:F381"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="16.14"/>
-    <col customWidth="1" min="2" max="2" width="38.86"/>
-    <col customWidth="1" min="3" max="3" width="38.0"/>
-    <col customWidth="1" min="4" max="4" width="62.14"/>
-    <col customWidth="1" min="5" max="5" width="31.43"/>
-    <col customWidth="1" min="6" max="11" width="8.71"/>
+    <col min="1" max="1" width="16.140625" customWidth="1"/>
+    <col min="2" max="2" width="38.85546875" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
+    <col min="4" max="4" width="62.140625" customWidth="1"/>
+    <col min="5" max="5" width="31.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" customWidth="1"/>
+    <col min="7" max="11" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2993,10 +3029,13 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="str">
-        <f t="shared" ref="A2:A380" si="1">ROW(A1)</f>
+      <c r="F1" s="1" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <f t="shared" ref="A2:A256" si="0">ROW(A1)</f>
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -3011,10 +3050,13 @@
       <c r="E2" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F2" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -3029,10 +3071,13 @@
       <c r="E3" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F3" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -3047,10 +3092,13 @@
       <c r="E4" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F4" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -3065,10 +3113,13 @@
       <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F5" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -3083,10 +3134,13 @@
       <c r="E6" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F6" s="2" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -3101,10 +3155,13 @@
       <c r="E7" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F7" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -3119,10 +3176,13 @@
       <c r="E8" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F8" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -3137,10 +3197,13 @@
       <c r="E9" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F9" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -3155,10 +3218,13 @@
       <c r="E10" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F10" s="2" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -3173,10 +3239,13 @@
       <c r="E11" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F11" s="2" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -3191,10 +3260,13 @@
       <c r="E12" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F12" s="2" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -3209,10 +3281,13 @@
       <c r="E13" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F13" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -3227,10 +3302,13 @@
       <c r="E14" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F14" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -3245,10 +3323,13 @@
       <c r="E15" s="2" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F15" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -3263,10 +3344,13 @@
       <c r="E16" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F16" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -3281,10 +3365,13 @@
       <c r="E17" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F17" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -3299,10 +3386,13 @@
       <c r="E18" s="2" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F18" s="2" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -3317,10 +3407,13 @@
       <c r="E19" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F19" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -3335,10 +3428,13 @@
       <c r="E20" s="2" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F20" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -3353,10 +3449,13 @@
       <c r="E21" s="2" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F21" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -3371,10 +3470,13 @@
       <c r="E22" s="2" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F22" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
@@ -3389,10 +3491,13 @@
       <c r="E23" s="2" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F23" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
@@ -3407,10 +3512,13 @@
       <c r="E24" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F24" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
@@ -3425,10 +3533,13 @@
       <c r="E25" s="2" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F25" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
@@ -3443,10 +3554,13 @@
       <c r="E26" s="2" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F26" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
@@ -3461,10 +3575,13 @@
       <c r="E27" s="2" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F27" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -3479,10 +3596,13 @@
       <c r="E28" s="2" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F28" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
@@ -3497,10 +3617,13 @@
       <c r="E29" s="2" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F29" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
@@ -3515,10 +3638,13 @@
       <c r="E30" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F30" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
@@ -3533,10 +3659,13 @@
       <c r="E31" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F31" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -3551,10 +3680,13 @@
       <c r="E32" s="2" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F32" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
@@ -3569,10 +3701,13 @@
       <c r="E33" s="2" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F33" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
@@ -3587,10 +3722,13 @@
       <c r="E34" s="2" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F34" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
@@ -3605,10 +3743,13 @@
       <c r="E35" s="2" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F35" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
@@ -3623,10 +3764,13 @@
       <c r="E36" s="2" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F36" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <f t="shared" si="0"/>
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
@@ -3641,10 +3785,13 @@
       <c r="E37" s="2" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F37" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
@@ -3659,10 +3806,13 @@
       <c r="E38" s="2" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F38" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <f t="shared" si="0"/>
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
@@ -3677,10 +3827,13 @@
       <c r="E39" s="2" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F39" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
@@ -3695,10 +3848,13 @@
       <c r="E40" s="2" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F40" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
@@ -3713,10 +3869,13 @@
       <c r="E41" s="2" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F41" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
@@ -3731,10 +3890,13 @@
       <c r="E42" s="2" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F42" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
@@ -3749,10 +3911,13 @@
       <c r="E43" s="2" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F43" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
@@ -3767,10 +3932,13 @@
       <c r="E44" s="2" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F44" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
@@ -3785,10 +3953,13 @@
       <c r="E45" s="2" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F45" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
@@ -3803,10 +3974,13 @@
       <c r="E46" s="2" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F46" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
@@ -3821,10 +3995,13 @@
       <c r="E47" s="2" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F47" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
@@ -3839,10 +4016,13 @@
       <c r="E48" s="2" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F48" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <f t="shared" si="0"/>
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
@@ -3857,10 +4037,13 @@
       <c r="E49" s="2" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F49" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
@@ -3875,10 +4058,13 @@
       <c r="E50" s="2" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F50" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
@@ -3893,10 +4079,13 @@
       <c r="E51" s="2" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F51" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
+        <f t="shared" si="0"/>
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
@@ -3911,10 +4100,13 @@
       <c r="E52" s="2" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F52" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="2">
+        <f t="shared" si="0"/>
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
@@ -3929,10 +4121,13 @@
       <c r="E53" s="2" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F53" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
+        <f t="shared" si="0"/>
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
@@ -3947,10 +4142,13 @@
       <c r="E54" s="2" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F54" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
+        <f t="shared" si="0"/>
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
@@ -3965,10 +4163,13 @@
       <c r="E55" s="2" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F55" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
+        <f t="shared" si="0"/>
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
@@ -3983,10 +4184,13 @@
       <c r="E56" s="2" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F56" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
+        <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
@@ -4001,10 +4205,13 @@
       <c r="E57" s="2" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F57" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
+        <f t="shared" si="0"/>
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
@@ -4019,10 +4226,13 @@
       <c r="E58" s="2" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F58" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2">
+        <f t="shared" si="0"/>
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
@@ -4037,10 +4247,13 @@
       <c r="E59" s="2" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F59" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
+        <f t="shared" si="0"/>
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
@@ -4055,10 +4268,13 @@
       <c r="E60" s="2" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F60" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
@@ -4073,10 +4289,13 @@
       <c r="E61" s="2" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F61" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <f t="shared" si="0"/>
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
@@ -4091,10 +4310,13 @@
       <c r="E62" s="2" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F62" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
+        <f t="shared" si="0"/>
         <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
@@ -4109,10 +4331,13 @@
       <c r="E63" s="2" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F63" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
+        <f t="shared" si="0"/>
         <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
@@ -4127,10 +4352,13 @@
       <c r="E64" s="2" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F64" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
+        <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="B65" s="2" t="s">
@@ -4145,10 +4373,13 @@
       <c r="E65" s="2" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F65" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
+        <f t="shared" si="0"/>
         <v>65</v>
       </c>
       <c r="B66" s="2" t="s">
@@ -4163,10 +4394,13 @@
       <c r="E66" s="2" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F66" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="2">
+        <f t="shared" si="0"/>
         <v>66</v>
       </c>
       <c r="B67" s="2" t="s">
@@ -4181,10 +4415,13 @@
       <c r="E67" s="2" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F67" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
+        <f t="shared" si="0"/>
         <v>67</v>
       </c>
       <c r="B68" s="2" t="s">
@@ -4199,10 +4436,13 @@
       <c r="E68" s="2" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F68" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="2">
+        <f t="shared" si="0"/>
         <v>68</v>
       </c>
       <c r="B69" s="2" t="s">
@@ -4217,10 +4457,13 @@
       <c r="E69" s="2" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F69" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
+        <f t="shared" si="0"/>
         <v>69</v>
       </c>
       <c r="B70" s="2" t="s">
@@ -4235,10 +4478,13 @@
       <c r="E70" s="2" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F70" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="2">
+        <f t="shared" si="0"/>
         <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
@@ -4253,10 +4499,13 @@
       <c r="E71" s="2" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F71" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="2">
+        <f t="shared" si="0"/>
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
@@ -4271,10 +4520,13 @@
       <c r="E72" s="2" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F72" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="2">
+        <f t="shared" si="0"/>
         <v>72</v>
       </c>
       <c r="B73" s="2" t="s">
@@ -4289,10 +4541,13 @@
       <c r="E73" s="2" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F73" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="2">
+        <f t="shared" si="0"/>
         <v>73</v>
       </c>
       <c r="B74" s="2" t="s">
@@ -4307,10 +4562,13 @@
       <c r="E74" s="2" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F74" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="2">
+        <f t="shared" si="0"/>
         <v>74</v>
       </c>
       <c r="B75" s="2" t="s">
@@ -4325,10 +4583,13 @@
       <c r="E75" s="2" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F75" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="2">
+        <f t="shared" si="0"/>
         <v>75</v>
       </c>
       <c r="B76" s="2" t="s">
@@ -4343,10 +4604,13 @@
       <c r="E76" s="2" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F76" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="2">
+        <f t="shared" si="0"/>
         <v>76</v>
       </c>
       <c r="B77" s="2" t="s">
@@ -4361,10 +4625,13 @@
       <c r="E77" s="2" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F77" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
+        <f t="shared" si="0"/>
         <v>77</v>
       </c>
       <c r="B78" s="2" t="s">
@@ -4379,10 +4646,13 @@
       <c r="E78" s="2" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F78" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="2">
+        <f t="shared" si="0"/>
         <v>78</v>
       </c>
       <c r="B79" s="2" t="s">
@@ -4397,10 +4667,13 @@
       <c r="E79" s="2" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F79" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="2">
+        <f t="shared" si="0"/>
         <v>79</v>
       </c>
       <c r="B80" s="2" t="s">
@@ -4415,10 +4688,13 @@
       <c r="E80" s="2" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F80" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="2">
+        <f t="shared" si="0"/>
         <v>80</v>
       </c>
       <c r="B81" s="2" t="s">
@@ -4433,10 +4709,13 @@
       <c r="E81" s="2" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F81" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="2">
+        <f t="shared" si="0"/>
         <v>81</v>
       </c>
       <c r="B82" s="2" t="s">
@@ -4451,10 +4730,13 @@
       <c r="E82" s="2" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F82" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="2">
+        <f t="shared" si="0"/>
         <v>82</v>
       </c>
       <c r="B83" s="2" t="s">
@@ -4469,10 +4751,13 @@
       <c r="E83" s="2" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F83" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="2">
+        <f t="shared" si="0"/>
         <v>83</v>
       </c>
       <c r="B84" s="2" t="s">
@@ -4487,10 +4772,13 @@
       <c r="E84" s="2" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F84" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="2">
+        <f t="shared" si="0"/>
         <v>84</v>
       </c>
       <c r="B85" s="2" t="s">
@@ -4505,10 +4793,13 @@
       <c r="E85" s="2" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F85" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="2">
+        <f t="shared" si="0"/>
         <v>85</v>
       </c>
       <c r="B86" s="2" t="s">
@@ -4523,10 +4814,13 @@
       <c r="E86" s="2" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F86" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="2">
+        <f t="shared" si="0"/>
         <v>86</v>
       </c>
       <c r="B87" s="2" t="s">
@@ -4541,10 +4835,13 @@
       <c r="E87" s="2" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F87" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="2">
+        <f t="shared" si="0"/>
         <v>87</v>
       </c>
       <c r="B88" s="2" t="s">
@@ -4559,10 +4856,13 @@
       <c r="E88" s="2" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F88" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="2">
+        <f t="shared" si="0"/>
         <v>88</v>
       </c>
       <c r="B89" s="2" t="s">
@@ -4577,10 +4877,13 @@
       <c r="E89" s="2" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F89" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="2">
+        <f t="shared" si="0"/>
         <v>89</v>
       </c>
       <c r="B90" s="2" t="s">
@@ -4595,10 +4898,13 @@
       <c r="E90" s="2" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F90" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="2">
+        <f t="shared" si="0"/>
         <v>90</v>
       </c>
       <c r="B91" s="2" t="s">
@@ -4613,10 +4919,13 @@
       <c r="E91" s="2" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F91" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="2">
+        <f t="shared" si="0"/>
         <v>91</v>
       </c>
       <c r="B92" s="2" t="s">
@@ -4631,10 +4940,13 @@
       <c r="E92" s="2" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F92" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="2">
+        <f t="shared" si="0"/>
         <v>92</v>
       </c>
       <c r="B93" s="2" t="s">
@@ -4649,10 +4961,13 @@
       <c r="E93" s="2" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F93" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="2">
+        <f t="shared" si="0"/>
         <v>93</v>
       </c>
       <c r="B94" s="2" t="s">
@@ -4667,10 +4982,13 @@
       <c r="E94" s="2" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F94" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="2">
+        <f t="shared" si="0"/>
         <v>94</v>
       </c>
       <c r="B95" s="2" t="s">
@@ -4685,10 +5003,13 @@
       <c r="E95" s="2" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F95" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="2">
+        <f t="shared" si="0"/>
         <v>95</v>
       </c>
       <c r="B96" s="2" t="s">
@@ -4703,10 +5024,13 @@
       <c r="E96" s="2" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F96" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="2">
+        <f t="shared" si="0"/>
         <v>96</v>
       </c>
       <c r="B97" s="2" t="s">
@@ -4721,10 +5045,13 @@
       <c r="E97" s="2" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F97" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="2">
+        <f t="shared" si="0"/>
         <v>97</v>
       </c>
       <c r="B98" s="2" t="s">
@@ -4739,10 +5066,13 @@
       <c r="E98" s="2" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F98" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="2">
+        <f t="shared" si="0"/>
         <v>98</v>
       </c>
       <c r="B99" s="2" t="s">
@@ -4757,10 +5087,13 @@
       <c r="E99" s="2" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F99" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="2">
+        <f t="shared" si="0"/>
         <v>99</v>
       </c>
       <c r="B100" s="2" t="s">
@@ -4775,10 +5108,13 @@
       <c r="E100" s="2" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F100" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="2">
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="B101" s="2" t="s">
@@ -4793,10 +5129,13 @@
       <c r="E101" s="2" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F101" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="2">
+        <f t="shared" si="0"/>
         <v>101</v>
       </c>
       <c r="B102" s="2" t="s">
@@ -4811,10 +5150,13 @@
       <c r="E102" s="2" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F102" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="2">
+        <f t="shared" si="0"/>
         <v>102</v>
       </c>
       <c r="B103" s="2" t="s">
@@ -4829,10 +5171,13 @@
       <c r="E103" s="2" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F103" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="2">
+        <f t="shared" si="0"/>
         <v>103</v>
       </c>
       <c r="B104" s="2" t="s">
@@ -4847,10 +5192,13 @@
       <c r="E104" s="2" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F104" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="2">
+        <f t="shared" si="0"/>
         <v>104</v>
       </c>
       <c r="B105" s="2" t="s">
@@ -4865,10 +5213,13 @@
       <c r="E105" s="2" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F105" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="2">
+        <f t="shared" si="0"/>
         <v>105</v>
       </c>
       <c r="B106" s="2" t="s">
@@ -4883,10 +5234,13 @@
       <c r="E106" s="2" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F106" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="2">
+        <f t="shared" si="0"/>
         <v>106</v>
       </c>
       <c r="B107" s="2" t="s">
@@ -4901,10 +5255,13 @@
       <c r="E107" s="2" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F107" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="2">
+        <f t="shared" si="0"/>
         <v>107</v>
       </c>
       <c r="B108" s="2" t="s">
@@ -4919,10 +5276,13 @@
       <c r="E108" s="2" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F108" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="2">
+        <f t="shared" si="0"/>
         <v>108</v>
       </c>
       <c r="B109" s="2" t="s">
@@ -4937,10 +5297,13 @@
       <c r="E109" s="2" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F109" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="2">
+        <f t="shared" si="0"/>
         <v>109</v>
       </c>
       <c r="B110" s="2" t="s">
@@ -4955,10 +5318,13 @@
       <c r="E110" s="2" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F110" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="2">
+        <f t="shared" si="0"/>
         <v>110</v>
       </c>
       <c r="B111" s="2" t="s">
@@ -4973,10 +5339,13 @@
       <c r="E111" s="2" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F111" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="2">
+        <f t="shared" si="0"/>
         <v>111</v>
       </c>
       <c r="B112" s="2" t="s">
@@ -4991,10 +5360,13 @@
       <c r="E112" s="2" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F112" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="2">
+        <f t="shared" si="0"/>
         <v>112</v>
       </c>
       <c r="B113" s="2" t="s">
@@ -5009,10 +5381,13 @@
       <c r="E113" s="2" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F113" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="2">
+        <f t="shared" si="0"/>
         <v>113</v>
       </c>
       <c r="B114" s="2" t="s">
@@ -5027,10 +5402,13 @@
       <c r="E114" s="2" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F114" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="2">
+        <f t="shared" si="0"/>
         <v>114</v>
       </c>
       <c r="B115" s="2" t="s">
@@ -5045,10 +5423,13 @@
       <c r="E115" s="2" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F115" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="2">
+        <f t="shared" si="0"/>
         <v>115</v>
       </c>
       <c r="B116" s="2" t="s">
@@ -5063,10 +5444,13 @@
       <c r="E116" s="2" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F116" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="2">
+        <f t="shared" si="0"/>
         <v>116</v>
       </c>
       <c r="B117" s="2" t="s">
@@ -5081,10 +5465,13 @@
       <c r="E117" s="2" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F117" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="2">
+        <f t="shared" si="0"/>
         <v>117</v>
       </c>
       <c r="B118" s="2" t="s">
@@ -5099,10 +5486,13 @@
       <c r="E118" s="2" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F118" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="2">
+        <f t="shared" si="0"/>
         <v>118</v>
       </c>
       <c r="B119" s="2" t="s">
@@ -5117,10 +5507,13 @@
       <c r="E119" s="2" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F119" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="2">
+        <f t="shared" si="0"/>
         <v>119</v>
       </c>
       <c r="B120" s="2" t="s">
@@ -5135,10 +5528,13 @@
       <c r="E120" s="2" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F120" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="2">
+        <f t="shared" si="0"/>
         <v>120</v>
       </c>
       <c r="B121" s="2" t="s">
@@ -5153,10 +5549,13 @@
       <c r="E121" s="2" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F121" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="2">
+        <f t="shared" si="0"/>
         <v>121</v>
       </c>
       <c r="B122" s="2" t="s">
@@ -5171,10 +5570,13 @@
       <c r="E122" s="2" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F122" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="2">
+        <f t="shared" si="0"/>
         <v>122</v>
       </c>
       <c r="B123" s="2" t="s">
@@ -5189,10 +5591,13 @@
       <c r="E123" s="2" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F123" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="2">
+        <f t="shared" si="0"/>
         <v>123</v>
       </c>
       <c r="B124" s="2" t="s">
@@ -5207,10 +5612,13 @@
       <c r="E124" s="2" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F124" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="2">
+        <f t="shared" si="0"/>
         <v>124</v>
       </c>
       <c r="B125" s="2" t="s">
@@ -5225,10 +5633,13 @@
       <c r="E125" s="2" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F125" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="2">
+        <f t="shared" si="0"/>
         <v>125</v>
       </c>
       <c r="B126" s="2" t="s">
@@ -5243,10 +5654,13 @@
       <c r="E126" s="2" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F126" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="2">
+        <f t="shared" si="0"/>
         <v>126</v>
       </c>
       <c r="B127" s="2" t="s">
@@ -5261,10 +5675,13 @@
       <c r="E127" s="2" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F127" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="2">
+        <f t="shared" si="0"/>
         <v>127</v>
       </c>
       <c r="B128" s="2" t="s">
@@ -5279,10 +5696,13 @@
       <c r="E128" s="2" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F128" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="2">
+        <f t="shared" si="0"/>
         <v>128</v>
       </c>
       <c r="B129" s="2" t="s">
@@ -5297,10 +5717,13 @@
       <c r="E129" s="2" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F129" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="2">
+        <f t="shared" si="0"/>
         <v>129</v>
       </c>
       <c r="B130" s="2" t="s">
@@ -5315,10 +5738,13 @@
       <c r="E130" s="2" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F130" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="2">
+        <f t="shared" si="0"/>
         <v>130</v>
       </c>
       <c r="B131" s="2" t="s">
@@ -5333,10 +5759,13 @@
       <c r="E131" s="2" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F131" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="2">
+        <f t="shared" si="0"/>
         <v>131</v>
       </c>
       <c r="B132" s="2" t="s">
@@ -5351,10 +5780,13 @@
       <c r="E132" s="2" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F132" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="2">
+        <f t="shared" si="0"/>
         <v>132</v>
       </c>
       <c r="B133" s="2" t="s">
@@ -5369,10 +5801,13 @@
       <c r="E133" s="2" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F133" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="2">
+        <f t="shared" si="0"/>
         <v>133</v>
       </c>
       <c r="B134" s="2" t="s">
@@ -5387,10 +5822,13 @@
       <c r="E134" s="2" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F134" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="2">
+        <f t="shared" si="0"/>
         <v>134</v>
       </c>
       <c r="B135" s="2" t="s">
@@ -5405,10 +5843,13 @@
       <c r="E135" s="2" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F135" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="2">
+        <f t="shared" si="0"/>
         <v>135</v>
       </c>
       <c r="B136" s="2" t="s">
@@ -5423,10 +5864,13 @@
       <c r="E136" s="2" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F136" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="2">
+        <f t="shared" si="0"/>
         <v>136</v>
       </c>
       <c r="B137" s="2" t="s">
@@ -5441,10 +5885,13 @@
       <c r="E137" s="2" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F137" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="2">
+        <f t="shared" si="0"/>
         <v>137</v>
       </c>
       <c r="B138" s="2" t="s">
@@ -5459,10 +5906,13 @@
       <c r="E138" s="2" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F138" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="2">
+        <f t="shared" si="0"/>
         <v>138</v>
       </c>
       <c r="B139" s="2" t="s">
@@ -5477,10 +5927,13 @@
       <c r="E139" s="2" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F139" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="2">
+        <f t="shared" si="0"/>
         <v>139</v>
       </c>
       <c r="B140" s="2" t="s">
@@ -5495,10 +5948,13 @@
       <c r="E140" s="2" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F140" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="2">
+        <f t="shared" si="0"/>
         <v>140</v>
       </c>
       <c r="B141" s="2" t="s">
@@ -5513,10 +5969,13 @@
       <c r="E141" s="2" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F141" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="2">
+        <f t="shared" si="0"/>
         <v>141</v>
       </c>
       <c r="B142" s="2" t="s">
@@ -5531,10 +5990,13 @@
       <c r="E142" s="2" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F142" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="2">
+        <f t="shared" si="0"/>
         <v>142</v>
       </c>
       <c r="B143" s="2" t="s">
@@ -5549,10 +6011,13 @@
       <c r="E143" s="2" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F143" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="2">
+        <f t="shared" si="0"/>
         <v>143</v>
       </c>
       <c r="B144" s="2" t="s">
@@ -5567,10 +6032,13 @@
       <c r="E144" s="2" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F144" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="2">
+        <f t="shared" si="0"/>
         <v>144</v>
       </c>
       <c r="B145" s="2" t="s">
@@ -5585,10 +6053,13 @@
       <c r="E145" s="2" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F145" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="2">
+        <f t="shared" si="0"/>
         <v>145</v>
       </c>
       <c r="B146" s="2" t="s">
@@ -5603,10 +6074,13 @@
       <c r="E146" s="2" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F146" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="2">
+        <f t="shared" si="0"/>
         <v>146</v>
       </c>
       <c r="B147" s="2" t="s">
@@ -5621,10 +6095,13 @@
       <c r="E147" s="2" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F147" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="2">
+        <f t="shared" si="0"/>
         <v>147</v>
       </c>
       <c r="B148" s="2" t="s">
@@ -5639,10 +6116,13 @@
       <c r="E148" s="2" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F148" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="2">
+        <f t="shared" si="0"/>
         <v>148</v>
       </c>
       <c r="B149" s="2" t="s">
@@ -5657,10 +6137,13 @@
       <c r="E149" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F149" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="2">
+        <f t="shared" si="0"/>
         <v>149</v>
       </c>
       <c r="B150" s="2" t="s">
@@ -5675,10 +6158,13 @@
       <c r="E150" s="2" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F150" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="2">
+        <f t="shared" si="0"/>
         <v>150</v>
       </c>
       <c r="B151" s="2" t="s">
@@ -5693,10 +6179,13 @@
       <c r="E151" s="2" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F151" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="2">
+        <f t="shared" si="0"/>
         <v>151</v>
       </c>
       <c r="B152" s="2" t="s">
@@ -5711,10 +6200,13 @@
       <c r="E152" s="2" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F152" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="2">
+        <f t="shared" si="0"/>
         <v>152</v>
       </c>
       <c r="B153" s="2" t="s">
@@ -5729,10 +6221,13 @@
       <c r="E153" s="2" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F153" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="2">
+        <f t="shared" si="0"/>
         <v>153</v>
       </c>
       <c r="B154" s="2" t="s">
@@ -5747,10 +6242,13 @@
       <c r="E154" s="2" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F154" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="2">
+        <f t="shared" si="0"/>
         <v>154</v>
       </c>
       <c r="B155" s="2" t="s">
@@ -5765,10 +6263,13 @@
       <c r="E155" s="2" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F155" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="2">
+        <f t="shared" si="0"/>
         <v>155</v>
       </c>
       <c r="B156" s="2" t="s">
@@ -5783,10 +6284,13 @@
       <c r="E156" s="2" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F156" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="2">
+        <f t="shared" si="0"/>
         <v>156</v>
       </c>
       <c r="B157" s="2" t="s">
@@ -5801,10 +6305,13 @@
       <c r="E157" s="2" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F157" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="2">
+        <f t="shared" si="0"/>
         <v>157</v>
       </c>
       <c r="B158" s="2" t="s">
@@ -5819,10 +6326,13 @@
       <c r="E158" s="2" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F158" s="2" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="2">
+        <f t="shared" si="0"/>
         <v>158</v>
       </c>
       <c r="B159" s="2" t="s">
@@ -5837,10 +6347,13 @@
       <c r="E159" s="2" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F159" s="2" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="2">
+        <f t="shared" si="0"/>
         <v>159</v>
       </c>
       <c r="B160" s="2" t="s">
@@ -5855,10 +6368,13 @@
       <c r="E160" s="2" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F160" s="2" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="2">
+        <f t="shared" si="0"/>
         <v>160</v>
       </c>
       <c r="B161" s="2" t="s">
@@ -5873,10 +6389,13 @@
       <c r="E161" s="2" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F161" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="2">
+        <f t="shared" si="0"/>
         <v>161</v>
       </c>
       <c r="B162" s="2" t="s">
@@ -5891,10 +6410,13 @@
       <c r="E162" s="2" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="163" ht="15.75" customHeight="1">
-      <c r="A163" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F162" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="2">
+        <f t="shared" si="0"/>
         <v>162</v>
       </c>
       <c r="B163" s="2" t="s">
@@ -5909,10 +6431,13 @@
       <c r="E163" s="2" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F163" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="2">
+        <f t="shared" si="0"/>
         <v>163</v>
       </c>
       <c r="B164" s="2" t="s">
@@ -5927,10 +6452,13 @@
       <c r="E164" s="2" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F164" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="2">
+        <f t="shared" si="0"/>
         <v>164</v>
       </c>
       <c r="B165" s="2" t="s">
@@ -5945,10 +6473,13 @@
       <c r="E165" s="2" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F165" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="2">
+        <f t="shared" si="0"/>
         <v>165</v>
       </c>
       <c r="B166" s="2" t="s">
@@ -5963,10 +6494,13 @@
       <c r="E166" s="2" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="167" ht="15.75" customHeight="1">
-      <c r="A167" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F166" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="2">
+        <f t="shared" si="0"/>
         <v>166</v>
       </c>
       <c r="B167" s="2" t="s">
@@ -5981,10 +6515,13 @@
       <c r="E167" s="2" t="s">
         <v>392</v>
       </c>
-    </row>
-    <row r="168" ht="15.75" customHeight="1">
-      <c r="A168" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F167" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="2">
+        <f t="shared" si="0"/>
         <v>167</v>
       </c>
       <c r="B168" s="2" t="s">
@@ -5999,10 +6536,13 @@
       <c r="E168" s="2" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="169" ht="15.75" customHeight="1">
-      <c r="A169" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F168" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="2">
+        <f t="shared" si="0"/>
         <v>168</v>
       </c>
       <c r="B169" s="2" t="s">
@@ -6017,10 +6557,13 @@
       <c r="E169" s="2" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="170" ht="15.75" customHeight="1">
-      <c r="A170" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F169" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A170" s="2">
+        <f t="shared" si="0"/>
         <v>169</v>
       </c>
       <c r="B170" s="2" t="s">
@@ -6035,10 +6578,13 @@
       <c r="E170" s="2" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F170" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="2">
+        <f t="shared" si="0"/>
         <v>170</v>
       </c>
       <c r="B171" s="2" t="s">
@@ -6053,10 +6599,13 @@
       <c r="E171" s="2" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F171" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A172" s="2">
+        <f t="shared" si="0"/>
         <v>171</v>
       </c>
       <c r="B172" s="2" t="s">
@@ -6071,10 +6620,13 @@
       <c r="E172" s="2" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="173" ht="15.75" customHeight="1">
-      <c r="A173" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F172" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A173" s="2">
+        <f t="shared" si="0"/>
         <v>172</v>
       </c>
       <c r="B173" s="2" t="s">
@@ -6089,10 +6641,13 @@
       <c r="E173" s="2" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="174" ht="15.75" customHeight="1">
-      <c r="A174" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F173" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="2">
+        <f t="shared" si="0"/>
         <v>173</v>
       </c>
       <c r="B174" s="2" t="s">
@@ -6107,10 +6662,13 @@
       <c r="E174" s="2" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="175" ht="15.75" customHeight="1">
-      <c r="A175" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F174" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A175" s="2">
+        <f t="shared" si="0"/>
         <v>174</v>
       </c>
       <c r="B175" s="2" t="s">
@@ -6125,10 +6683,13 @@
       <c r="E175" s="2" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="176" ht="15.75" customHeight="1">
-      <c r="A176" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F175" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A176" s="2">
+        <f t="shared" si="0"/>
         <v>175</v>
       </c>
       <c r="B176" s="2" t="s">
@@ -6143,10 +6704,13 @@
       <c r="E176" s="2" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="177" ht="15.75" customHeight="1">
-      <c r="A177" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F176" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="2">
+        <f t="shared" si="0"/>
         <v>176</v>
       </c>
       <c r="B177" s="2" t="s">
@@ -6161,10 +6725,13 @@
       <c r="E177" s="2" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="178" ht="15.75" customHeight="1">
-      <c r="A178" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F177" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A178" s="2">
+        <f t="shared" si="0"/>
         <v>177</v>
       </c>
       <c r="B178" s="2" t="s">
@@ -6179,10 +6746,13 @@
       <c r="E178" s="2" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="179" ht="15.75" customHeight="1">
-      <c r="A179" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F178" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A179" s="2">
+        <f t="shared" si="0"/>
         <v>178</v>
       </c>
       <c r="B179" s="2" t="s">
@@ -6197,10 +6767,13 @@
       <c r="E179" s="2" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="180" ht="15.75" customHeight="1">
-      <c r="A180" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F179" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="2">
+        <f t="shared" si="0"/>
         <v>179</v>
       </c>
       <c r="B180" s="2" t="s">
@@ -6215,10 +6788,13 @@
       <c r="E180" s="2" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="181" ht="15.75" customHeight="1">
-      <c r="A181" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F180" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A181" s="2">
+        <f t="shared" si="0"/>
         <v>180</v>
       </c>
       <c r="B181" s="2" t="s">
@@ -6233,10 +6809,13 @@
       <c r="E181" s="2" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="182" ht="15.75" customHeight="1">
-      <c r="A182" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F181" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A182" s="2">
+        <f t="shared" si="0"/>
         <v>181</v>
       </c>
       <c r="B182" s="2" t="s">
@@ -6251,10 +6830,13 @@
       <c r="E182" s="2" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="183" ht="15.75" customHeight="1">
-      <c r="A183" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F182" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="2">
+        <f t="shared" si="0"/>
         <v>182</v>
       </c>
       <c r="B183" s="2" t="s">
@@ -6269,10 +6851,13 @@
       <c r="E183" s="2" t="s">
         <v>429</v>
       </c>
-    </row>
-    <row r="184" ht="15.75" customHeight="1">
-      <c r="A184" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F183" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A184" s="2">
+        <f t="shared" si="0"/>
         <v>183</v>
       </c>
       <c r="B184" s="2" t="s">
@@ -6287,10 +6872,13 @@
       <c r="E184" s="2" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="185" ht="15.75" customHeight="1">
-      <c r="A185" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F184" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="2">
+        <f t="shared" si="0"/>
         <v>184</v>
       </c>
       <c r="B185" s="2" t="s">
@@ -6305,10 +6893,13 @@
       <c r="E185" s="2" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="186" ht="15.75" customHeight="1">
-      <c r="A186" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F185" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="2">
+        <f t="shared" si="0"/>
         <v>185</v>
       </c>
       <c r="B186" s="2" t="s">
@@ -6323,10 +6914,13 @@
       <c r="E186" s="2" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="187" ht="15.75" customHeight="1">
-      <c r="A187" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F186" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="2">
+        <f t="shared" si="0"/>
         <v>186</v>
       </c>
       <c r="B187" s="2" t="s">
@@ -6341,10 +6935,13 @@
       <c r="E187" s="2" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="188" ht="15.75" customHeight="1">
-      <c r="A188" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F187" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="2">
+        <f t="shared" si="0"/>
         <v>187</v>
       </c>
       <c r="B188" s="2" t="s">
@@ -6359,10 +6956,13 @@
       <c r="E188" s="2" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="189" ht="15.75" customHeight="1">
-      <c r="A189" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F188" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A189" s="2">
+        <f t="shared" si="0"/>
         <v>188</v>
       </c>
       <c r="B189" s="2" t="s">
@@ -6377,10 +6977,13 @@
       <c r="E189" s="2" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="190" ht="15.75" customHeight="1">
-      <c r="A190" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F189" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="2">
+        <f t="shared" si="0"/>
         <v>189</v>
       </c>
       <c r="B190" s="2" t="s">
@@ -6395,10 +6998,13 @@
       <c r="E190" s="2" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="191" ht="15.75" customHeight="1">
-      <c r="A191" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F190" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A191" s="2">
+        <f t="shared" si="0"/>
         <v>190</v>
       </c>
       <c r="B191" s="2" t="s">
@@ -6413,10 +7019,13 @@
       <c r="E191" s="2" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="192" ht="15.75" customHeight="1">
-      <c r="A192" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F191" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A192" s="2">
+        <f t="shared" si="0"/>
         <v>191</v>
       </c>
       <c r="B192" s="2" t="s">
@@ -6431,10 +7040,13 @@
       <c r="E192" s="2" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="193" ht="15.75" customHeight="1">
-      <c r="A193" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F192" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A193" s="2">
+        <f t="shared" si="0"/>
         <v>192</v>
       </c>
       <c r="B193" s="2" t="s">
@@ -6449,10 +7061,13 @@
       <c r="E193" s="2" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="194" ht="15.75" customHeight="1">
-      <c r="A194" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F193" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A194" s="2">
+        <f t="shared" si="0"/>
         <v>193</v>
       </c>
       <c r="B194" s="2" t="s">
@@ -6467,10 +7082,13 @@
       <c r="E194" s="2" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="195" ht="15.75" customHeight="1">
-      <c r="A195" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F194" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A195" s="2">
+        <f t="shared" si="0"/>
         <v>194</v>
       </c>
       <c r="B195" s="2" t="s">
@@ -6485,10 +7103,13 @@
       <c r="E195" s="2" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="196" ht="15.75" customHeight="1">
-      <c r="A196" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F195" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A196" s="2">
+        <f t="shared" si="0"/>
         <v>195</v>
       </c>
       <c r="B196" s="2" t="s">
@@ -6503,10 +7124,13 @@
       <c r="E196" s="2" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="197" ht="15.75" customHeight="1">
-      <c r="A197" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F196" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A197" s="2">
+        <f t="shared" si="0"/>
         <v>196</v>
       </c>
       <c r="B197" s="2" t="s">
@@ -6521,10 +7145,13 @@
       <c r="E197" s="2" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="198" ht="15.75" customHeight="1">
-      <c r="A198" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F197" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A198" s="2">
+        <f t="shared" si="0"/>
         <v>197</v>
       </c>
       <c r="B198" s="2" t="s">
@@ -6539,10 +7166,13 @@
       <c r="E198" s="2" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="199" ht="15.75" customHeight="1">
-      <c r="A199" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F198" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A199" s="2">
+        <f t="shared" si="0"/>
         <v>198</v>
       </c>
       <c r="B199" s="2" t="s">
@@ -6557,10 +7187,13 @@
       <c r="E199" s="2" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="200" ht="15.75" customHeight="1">
-      <c r="A200" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F199" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A200" s="2">
+        <f t="shared" si="0"/>
         <v>199</v>
       </c>
       <c r="B200" s="2" t="s">
@@ -6575,10 +7208,13 @@
       <c r="E200" s="2" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="201" ht="15.75" customHeight="1">
-      <c r="A201" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F200" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A201" s="2">
+        <f t="shared" si="0"/>
         <v>200</v>
       </c>
       <c r="B201" s="2" t="s">
@@ -6593,10 +7229,13 @@
       <c r="E201" s="2" t="s">
         <v>469</v>
       </c>
-    </row>
-    <row r="202" ht="15.75" customHeight="1">
-      <c r="A202" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F201" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A202" s="2">
+        <f t="shared" si="0"/>
         <v>201</v>
       </c>
       <c r="B202" s="2" t="s">
@@ -6611,10 +7250,13 @@
       <c r="E202" s="2" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="203" ht="15.75" customHeight="1">
-      <c r="A203" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F202" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A203" s="2">
+        <f t="shared" si="0"/>
         <v>202</v>
       </c>
       <c r="B203" s="2" t="s">
@@ -6629,10 +7271,13 @@
       <c r="E203" s="2" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="204" ht="15.75" customHeight="1">
-      <c r="A204" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F203" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A204" s="2">
+        <f t="shared" si="0"/>
         <v>203</v>
       </c>
       <c r="B204" s="2" t="s">
@@ -6647,10 +7292,13 @@
       <c r="E204" s="2" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="205" ht="15.75" customHeight="1">
-      <c r="A205" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F204" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A205" s="2">
+        <f t="shared" si="0"/>
         <v>204</v>
       </c>
       <c r="B205" s="2" t="s">
@@ -6665,10 +7313,13 @@
       <c r="E205" s="2" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="206" ht="15.75" customHeight="1">
-      <c r="A206" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F205" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A206" s="2">
+        <f t="shared" si="0"/>
         <v>205</v>
       </c>
       <c r="B206" s="2" t="s">
@@ -6683,10 +7334,13 @@
       <c r="E206" s="2" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="207" ht="15.75" customHeight="1">
-      <c r="A207" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F206" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A207" s="2">
+        <f t="shared" si="0"/>
         <v>206</v>
       </c>
       <c r="B207" s="2" t="s">
@@ -6701,10 +7355,13 @@
       <c r="E207" s="2" t="s">
         <v>481</v>
       </c>
-    </row>
-    <row r="208" ht="15.75" customHeight="1">
-      <c r="A208" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F207" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A208" s="2">
+        <f t="shared" si="0"/>
         <v>207</v>
       </c>
       <c r="B208" s="2" t="s">
@@ -6719,10 +7376,13 @@
       <c r="E208" s="2" t="s">
         <v>483</v>
       </c>
-    </row>
-    <row r="209" ht="15.75" customHeight="1">
-      <c r="A209" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F208" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A209" s="2">
+        <f t="shared" si="0"/>
         <v>208</v>
       </c>
       <c r="B209" s="2" t="s">
@@ -6737,10 +7397,13 @@
       <c r="E209" s="2" t="s">
         <v>485</v>
       </c>
-    </row>
-    <row r="210" ht="15.75" customHeight="1">
-      <c r="A210" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F209" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A210" s="2">
+        <f t="shared" si="0"/>
         <v>209</v>
       </c>
       <c r="B210" s="2" t="s">
@@ -6755,10 +7418,13 @@
       <c r="E210" s="2" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="211" ht="15.75" customHeight="1">
-      <c r="A211" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F210" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A211" s="2">
+        <f t="shared" si="0"/>
         <v>210</v>
       </c>
       <c r="B211" s="2" t="s">
@@ -6773,10 +7439,13 @@
       <c r="E211" s="2" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="212" ht="15.75" customHeight="1">
-      <c r="A212" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F211" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A212" s="2">
+        <f t="shared" si="0"/>
         <v>211</v>
       </c>
       <c r="B212" s="2" t="s">
@@ -6791,10 +7460,13 @@
       <c r="E212" s="2" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="213" ht="15.75" customHeight="1">
-      <c r="A213" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F212" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A213" s="2">
+        <f t="shared" si="0"/>
         <v>212</v>
       </c>
       <c r="B213" s="2" t="s">
@@ -6809,10 +7481,13 @@
       <c r="E213" s="2" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="214" ht="15.75" customHeight="1">
-      <c r="A214" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F213" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A214" s="2">
+        <f t="shared" si="0"/>
         <v>213</v>
       </c>
       <c r="B214" s="2" t="s">
@@ -6827,10 +7502,13 @@
       <c r="E214" s="2" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="215" ht="15.75" customHeight="1">
-      <c r="A215" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F214" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A215" s="2">
+        <f t="shared" si="0"/>
         <v>214</v>
       </c>
       <c r="B215" s="2" t="s">
@@ -6845,10 +7523,13 @@
       <c r="E215" s="2" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="216" ht="15.75" customHeight="1">
-      <c r="A216" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F215" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A216" s="2">
+        <f t="shared" si="0"/>
         <v>215</v>
       </c>
       <c r="B216" s="2" t="s">
@@ -6863,10 +7544,13 @@
       <c r="E216" s="2" t="s">
         <v>500</v>
       </c>
-    </row>
-    <row r="217" ht="15.75" customHeight="1">
-      <c r="A217" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F216" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A217" s="2">
+        <f t="shared" si="0"/>
         <v>216</v>
       </c>
       <c r="B217" s="2" t="s">
@@ -6881,10 +7565,13 @@
       <c r="E217" s="2" t="s">
         <v>502</v>
       </c>
-    </row>
-    <row r="218" ht="15.75" customHeight="1">
-      <c r="A218" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F217" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A218" s="2">
+        <f t="shared" si="0"/>
         <v>217</v>
       </c>
       <c r="B218" s="2" t="s">
@@ -6899,10 +7586,13 @@
       <c r="E218" s="2" t="s">
         <v>505</v>
       </c>
-    </row>
-    <row r="219" ht="15.75" customHeight="1">
-      <c r="A219" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F218" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A219" s="2">
+        <f t="shared" si="0"/>
         <v>218</v>
       </c>
       <c r="B219" s="2" t="s">
@@ -6917,10 +7607,13 @@
       <c r="E219" s="2" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="220" ht="15.75" customHeight="1">
-      <c r="A220" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F219" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A220" s="2">
+        <f t="shared" si="0"/>
         <v>219</v>
       </c>
       <c r="B220" s="2" t="s">
@@ -6935,10 +7628,13 @@
       <c r="E220" s="2" t="s">
         <v>509</v>
       </c>
-    </row>
-    <row r="221" ht="15.75" customHeight="1">
-      <c r="A221" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F220" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A221" s="2">
+        <f t="shared" si="0"/>
         <v>220</v>
       </c>
       <c r="B221" s="2" t="s">
@@ -6953,10 +7649,13 @@
       <c r="E221" s="2" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="222" ht="15.75" customHeight="1">
-      <c r="A222" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F221" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A222" s="2">
+        <f t="shared" si="0"/>
         <v>221</v>
       </c>
       <c r="B222" s="2" t="s">
@@ -6971,10 +7670,13 @@
       <c r="E222" s="2" t="s">
         <v>513</v>
       </c>
-    </row>
-    <row r="223" ht="15.75" customHeight="1">
-      <c r="A223" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F222" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A223" s="2">
+        <f t="shared" si="0"/>
         <v>222</v>
       </c>
       <c r="B223" s="2" t="s">
@@ -6989,10 +7691,13 @@
       <c r="E223" s="2" t="s">
         <v>515</v>
       </c>
-    </row>
-    <row r="224" ht="15.75" customHeight="1">
-      <c r="A224" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F223" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A224" s="2">
+        <f t="shared" si="0"/>
         <v>223</v>
       </c>
       <c r="B224" s="2" t="s">
@@ -7007,10 +7712,13 @@
       <c r="E224" s="2" t="s">
         <v>517</v>
       </c>
-    </row>
-    <row r="225" ht="15.75" customHeight="1">
-      <c r="A225" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F224" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A225" s="2">
+        <f t="shared" si="0"/>
         <v>224</v>
       </c>
       <c r="B225" s="2" t="s">
@@ -7025,10 +7733,13 @@
       <c r="E225" s="2" t="s">
         <v>519</v>
       </c>
-    </row>
-    <row r="226" ht="15.75" customHeight="1">
-      <c r="A226" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F225" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A226" s="2">
+        <f t="shared" si="0"/>
         <v>225</v>
       </c>
       <c r="B226" s="2" t="s">
@@ -7043,10 +7754,13 @@
       <c r="E226" s="2" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="227" ht="15.75" customHeight="1">
-      <c r="A227" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F226" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A227" s="2">
+        <f t="shared" si="0"/>
         <v>226</v>
       </c>
       <c r="B227" s="2" t="s">
@@ -7061,10 +7775,13 @@
       <c r="E227" s="2" t="s">
         <v>523</v>
       </c>
-    </row>
-    <row r="228" ht="15.75" customHeight="1">
-      <c r="A228" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F227" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A228" s="2">
+        <f t="shared" si="0"/>
         <v>227</v>
       </c>
       <c r="B228" s="2" t="s">
@@ -7079,10 +7796,13 @@
       <c r="E228" s="2" t="s">
         <v>525</v>
       </c>
-    </row>
-    <row r="229" ht="15.75" customHeight="1">
-      <c r="A229" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F228" s="2" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A229" s="2">
+        <f t="shared" si="0"/>
         <v>228</v>
       </c>
       <c r="B229" s="2" t="s">
@@ -7097,10 +7817,13 @@
       <c r="E229" s="2" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="230" ht="15.75" customHeight="1">
-      <c r="A230" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F229" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A230" s="2">
+        <f t="shared" si="0"/>
         <v>229</v>
       </c>
       <c r="B230" s="2" t="s">
@@ -7115,10 +7838,13 @@
       <c r="E230" s="2" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="231" ht="15.75" customHeight="1">
-      <c r="A231" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F230" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A231" s="2">
+        <f t="shared" si="0"/>
         <v>230</v>
       </c>
       <c r="B231" s="2" t="s">
@@ -7133,10 +7859,13 @@
       <c r="E231" s="2" t="s">
         <v>531</v>
       </c>
-    </row>
-    <row r="232" ht="15.75" customHeight="1">
-      <c r="A232" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F231" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A232" s="2">
+        <f t="shared" si="0"/>
         <v>231</v>
       </c>
       <c r="B232" s="2" t="s">
@@ -7151,10 +7880,13 @@
       <c r="E232" s="2" t="s">
         <v>533</v>
       </c>
-    </row>
-    <row r="233" ht="15.75" customHeight="1">
-      <c r="A233" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F232" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A233" s="2">
+        <f t="shared" si="0"/>
         <v>232</v>
       </c>
       <c r="B233" s="2" t="s">
@@ -7169,10 +7901,13 @@
       <c r="E233" s="2" t="s">
         <v>535</v>
       </c>
-    </row>
-    <row r="234" ht="15.75" customHeight="1">
-      <c r="A234" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F233" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A234" s="2">
+        <f t="shared" si="0"/>
         <v>233</v>
       </c>
       <c r="B234" s="2" t="s">
@@ -7187,10 +7922,13 @@
       <c r="E234" s="2" t="s">
         <v>537</v>
       </c>
-    </row>
-    <row r="235" ht="15.75" customHeight="1">
-      <c r="A235" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F234" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A235" s="2">
+        <f t="shared" si="0"/>
         <v>234</v>
       </c>
       <c r="B235" s="2" t="s">
@@ -7205,10 +7943,13 @@
       <c r="E235" s="2" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="236" ht="15.75" customHeight="1">
-      <c r="A236" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F235" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A236" s="2">
+        <f t="shared" si="0"/>
         <v>235</v>
       </c>
       <c r="B236" s="2" t="s">
@@ -7223,10 +7964,13 @@
       <c r="E236" s="2" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="237" ht="15.75" customHeight="1">
-      <c r="A237" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F236" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A237" s="2">
+        <f t="shared" si="0"/>
         <v>236</v>
       </c>
       <c r="B237" s="2" t="s">
@@ -7241,10 +7985,13 @@
       <c r="E237" s="2" t="s">
         <v>543</v>
       </c>
-    </row>
-    <row r="238" ht="15.75" customHeight="1">
-      <c r="A238" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F237" s="2" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A238" s="2">
+        <f t="shared" si="0"/>
         <v>237</v>
       </c>
       <c r="B238" s="2" t="s">
@@ -7259,10 +8006,13 @@
       <c r="E238" s="2" t="s">
         <v>545</v>
       </c>
-    </row>
-    <row r="239" ht="15.75" customHeight="1">
-      <c r="A239" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F238" s="2" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A239" s="2">
+        <f t="shared" si="0"/>
         <v>238</v>
       </c>
       <c r="B239" s="2" t="s">
@@ -7277,10 +8027,13 @@
       <c r="E239" s="2" t="s">
         <v>547</v>
       </c>
-    </row>
-    <row r="240" ht="15.75" customHeight="1">
-      <c r="A240" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F239" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A240" s="2">
+        <f t="shared" si="0"/>
         <v>239</v>
       </c>
       <c r="B240" s="2" t="s">
@@ -7295,10 +8048,13 @@
       <c r="E240" s="2" t="s">
         <v>549</v>
       </c>
-    </row>
-    <row r="241" ht="15.75" customHeight="1">
-      <c r="A241" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F240" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A241" s="2">
+        <f t="shared" si="0"/>
         <v>240</v>
       </c>
       <c r="B241" s="2" t="s">
@@ -7313,10 +8069,13 @@
       <c r="E241" s="2" t="s">
         <v>553</v>
       </c>
-    </row>
-    <row r="242" ht="15.75" customHeight="1">
-      <c r="A242" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F241" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A242" s="2">
+        <f t="shared" si="0"/>
         <v>241</v>
       </c>
       <c r="B242" s="2" t="s">
@@ -7331,10 +8090,13 @@
       <c r="E242" s="2" t="s">
         <v>557</v>
       </c>
-    </row>
-    <row r="243" ht="15.75" customHeight="1">
-      <c r="A243" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F242" s="2" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A243" s="2">
+        <f t="shared" si="0"/>
         <v>242</v>
       </c>
       <c r="B243" s="2" t="s">
@@ -7349,10 +8111,13 @@
       <c r="E243" s="2" t="s">
         <v>560</v>
       </c>
-    </row>
-    <row r="244" ht="15.75" customHeight="1">
-      <c r="A244" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F243" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A244" s="2">
+        <f t="shared" si="0"/>
         <v>243</v>
       </c>
       <c r="B244" s="2" t="s">
@@ -7367,10 +8132,13 @@
       <c r="E244" s="2" t="s">
         <v>562</v>
       </c>
-    </row>
-    <row r="245" ht="15.75" customHeight="1">
-      <c r="A245" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F244" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A245" s="2">
+        <f t="shared" si="0"/>
         <v>244</v>
       </c>
       <c r="B245" s="2" t="s">
@@ -7385,10 +8153,13 @@
       <c r="E245" s="2" t="s">
         <v>566</v>
       </c>
-    </row>
-    <row r="246" ht="15.75" customHeight="1">
-      <c r="A246" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F245" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A246" s="2">
+        <f t="shared" si="0"/>
         <v>245</v>
       </c>
       <c r="B246" s="2" t="s">
@@ -7403,10 +8174,13 @@
       <c r="E246" s="2" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="247" ht="15.75" customHeight="1">
-      <c r="A247" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F246" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A247" s="2">
+        <f t="shared" si="0"/>
         <v>246</v>
       </c>
       <c r="B247" s="2" t="s">
@@ -7421,10 +8195,13 @@
       <c r="E247" s="2" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="248" ht="15.75" customHeight="1">
-      <c r="A248" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F247" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A248" s="2">
+        <f t="shared" si="0"/>
         <v>247</v>
       </c>
       <c r="B248" s="2" t="s">
@@ -7439,10 +8216,13 @@
       <c r="E248" s="2" t="s">
         <v>574</v>
       </c>
-    </row>
-    <row r="249" ht="15.75" customHeight="1">
-      <c r="A249" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F248" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A249" s="2">
+        <f t="shared" si="0"/>
         <v>248</v>
       </c>
       <c r="B249" s="2" t="s">
@@ -7457,10 +8237,13 @@
       <c r="E249" s="2" t="s">
         <v>576</v>
       </c>
-    </row>
-    <row r="250" ht="15.75" customHeight="1">
-      <c r="A250" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F249" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A250" s="2">
+        <f t="shared" si="0"/>
         <v>249</v>
       </c>
       <c r="B250" s="2" t="s">
@@ -7475,10 +8258,13 @@
       <c r="E250" s="2" t="s">
         <v>580</v>
       </c>
-    </row>
-    <row r="251" ht="15.75" customHeight="1">
-      <c r="A251" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F250" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A251" s="2">
+        <f t="shared" si="0"/>
         <v>250</v>
       </c>
       <c r="B251" s="2" t="s">
@@ -7493,10 +8279,13 @@
       <c r="E251" s="2" t="s">
         <v>584</v>
       </c>
-    </row>
-    <row r="252" ht="15.75" customHeight="1">
-      <c r="A252" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F251" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A252" s="2">
+        <f t="shared" si="0"/>
         <v>251</v>
       </c>
       <c r="B252" s="2" t="s">
@@ -7511,10 +8300,13 @@
       <c r="E252" s="2" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="253" ht="15.75" customHeight="1">
-      <c r="A253" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F252" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A253" s="2">
+        <f t="shared" si="0"/>
         <v>252</v>
       </c>
       <c r="B253" s="2" t="s">
@@ -7529,10 +8321,13 @@
       <c r="E253" s="2" t="s">
         <v>588</v>
       </c>
-    </row>
-    <row r="254" ht="15.75" customHeight="1">
-      <c r="A254" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F253" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A254" s="2">
+        <f t="shared" si="0"/>
         <v>253</v>
       </c>
       <c r="B254" s="2" t="s">
@@ -7547,10 +8342,13 @@
       <c r="E254" s="2" t="s">
         <v>590</v>
       </c>
-    </row>
-    <row r="255" ht="15.75" customHeight="1">
-      <c r="A255" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F254" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A255" s="2">
+        <f t="shared" si="0"/>
         <v>254</v>
       </c>
       <c r="B255" s="2" t="s">
@@ -7565,10 +8363,13 @@
       <c r="E255" s="2" t="s">
         <v>592</v>
       </c>
-    </row>
-    <row r="256" ht="15.75" customHeight="1">
-      <c r="A256" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F255" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A256" s="2">
+        <f t="shared" si="0"/>
         <v>255</v>
       </c>
       <c r="B256" s="2" t="s">
@@ -7583,10 +8384,13 @@
       <c r="E256" s="2" t="s">
         <v>594</v>
       </c>
-    </row>
-    <row r="257" ht="15.75" customHeight="1">
-      <c r="A257" s="2" t="str">
-        <f t="shared" si="1"/>
+      <c r="F256" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A257" s="2">
+        <f t="shared" ref="A257:A381" si="1">ROW(A256)</f>
         <v>256</v>
       </c>
       <c r="B257" s="2" t="s">
@@ -7601,9 +8405,12 @@
       <c r="E257" s="2" t="s">
         <v>596</v>
       </c>
-    </row>
-    <row r="258" ht="15.75" customHeight="1">
-      <c r="A258" s="2" t="str">
+      <c r="F257" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A258" s="2">
         <f t="shared" si="1"/>
         <v>257</v>
       </c>
@@ -7619,9 +8426,12 @@
       <c r="E258" s="2" t="s">
         <v>598</v>
       </c>
-    </row>
-    <row r="259" ht="15.75" customHeight="1">
-      <c r="A259" s="2" t="str">
+      <c r="F258" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A259" s="2">
         <f t="shared" si="1"/>
         <v>258</v>
       </c>
@@ -7637,9 +8447,12 @@
       <c r="E259" s="2" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="260" ht="15.75" customHeight="1">
-      <c r="A260" s="2" t="str">
+      <c r="F259" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A260" s="2">
         <f t="shared" si="1"/>
         <v>259</v>
       </c>
@@ -7655,9 +8468,12 @@
       <c r="E260" s="2" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="261" ht="15.75" customHeight="1">
-      <c r="A261" s="2" t="str">
+      <c r="F260" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A261" s="2">
         <f t="shared" si="1"/>
         <v>260</v>
       </c>
@@ -7673,9 +8489,12 @@
       <c r="E261" s="2" t="s">
         <v>604</v>
       </c>
-    </row>
-    <row r="262" ht="15.75" customHeight="1">
-      <c r="A262" s="2" t="str">
+      <c r="F261" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A262" s="2">
         <f t="shared" si="1"/>
         <v>261</v>
       </c>
@@ -7691,9 +8510,12 @@
       <c r="E262" s="2" t="s">
         <v>606</v>
       </c>
-    </row>
-    <row r="263" ht="15.75" customHeight="1">
-      <c r="A263" s="2" t="str">
+      <c r="F262" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A263" s="2">
         <f t="shared" si="1"/>
         <v>262</v>
       </c>
@@ -7709,9 +8531,12 @@
       <c r="E263" s="2" t="s">
         <v>608</v>
       </c>
-    </row>
-    <row r="264" ht="15.75" customHeight="1">
-      <c r="A264" s="2" t="str">
+      <c r="F263" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A264" s="2">
         <f t="shared" si="1"/>
         <v>263</v>
       </c>
@@ -7727,9 +8552,12 @@
       <c r="E264" s="2" t="s">
         <v>610</v>
       </c>
-    </row>
-    <row r="265" ht="15.75" customHeight="1">
-      <c r="A265" s="2" t="str">
+      <c r="F264" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A265" s="2">
         <f t="shared" si="1"/>
         <v>264</v>
       </c>
@@ -7745,9 +8573,12 @@
       <c r="E265" s="2" t="s">
         <v>612</v>
       </c>
-    </row>
-    <row r="266" ht="15.75" customHeight="1">
-      <c r="A266" s="2" t="str">
+      <c r="F265" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A266" s="2">
         <f t="shared" si="1"/>
         <v>265</v>
       </c>
@@ -7763,9 +8594,12 @@
       <c r="E266" s="2" t="s">
         <v>614</v>
       </c>
-    </row>
-    <row r="267" ht="15.75" customHeight="1">
-      <c r="A267" s="2" t="str">
+      <c r="F266" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A267" s="2">
         <f t="shared" si="1"/>
         <v>266</v>
       </c>
@@ -7781,9 +8615,12 @@
       <c r="E267" s="2" t="s">
         <v>616</v>
       </c>
-    </row>
-    <row r="268" ht="15.75" customHeight="1">
-      <c r="A268" s="2" t="str">
+      <c r="F267" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A268" s="2">
         <f t="shared" si="1"/>
         <v>267</v>
       </c>
@@ -7799,9 +8636,12 @@
       <c r="E268" s="2" t="s">
         <v>618</v>
       </c>
-    </row>
-    <row r="269" ht="15.75" customHeight="1">
-      <c r="A269" s="2" t="str">
+      <c r="F268" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A269" s="2">
         <f t="shared" si="1"/>
         <v>268</v>
       </c>
@@ -7817,9 +8657,12 @@
       <c r="E269" s="2" t="s">
         <v>620</v>
       </c>
-    </row>
-    <row r="270" ht="15.75" customHeight="1">
-      <c r="A270" s="2" t="str">
+      <c r="F269" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A270" s="2">
         <f t="shared" si="1"/>
         <v>269</v>
       </c>
@@ -7835,9 +8678,12 @@
       <c r="E270" s="2" t="s">
         <v>622</v>
       </c>
-    </row>
-    <row r="271" ht="15.75" customHeight="1">
-      <c r="A271" s="2" t="str">
+      <c r="F270" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A271" s="2">
         <f t="shared" si="1"/>
         <v>270</v>
       </c>
@@ -7853,9 +8699,12 @@
       <c r="E271" s="2" t="s">
         <v>625</v>
       </c>
-    </row>
-    <row r="272" ht="15.75" customHeight="1">
-      <c r="A272" s="2" t="str">
+      <c r="F271" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A272" s="2">
         <f t="shared" si="1"/>
         <v>271</v>
       </c>
@@ -7871,9 +8720,12 @@
       <c r="E272" s="2" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="273" ht="15.75" customHeight="1">
-      <c r="A273" s="2" t="str">
+      <c r="F272" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A273" s="2">
         <f t="shared" si="1"/>
         <v>272</v>
       </c>
@@ -7889,9 +8741,12 @@
       <c r="E273" s="2" t="s">
         <v>629</v>
       </c>
-    </row>
-    <row r="274" ht="15.75" customHeight="1">
-      <c r="A274" s="2" t="str">
+      <c r="F273" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A274" s="2">
         <f t="shared" si="1"/>
         <v>273</v>
       </c>
@@ -7907,9 +8762,12 @@
       <c r="E274" s="2" t="s">
         <v>631</v>
       </c>
-    </row>
-    <row r="275" ht="15.75" customHeight="1">
-      <c r="A275" s="2" t="str">
+      <c r="F274" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A275" s="2">
         <f t="shared" si="1"/>
         <v>274</v>
       </c>
@@ -7925,9 +8783,12 @@
       <c r="E275" s="2" t="s">
         <v>633</v>
       </c>
-    </row>
-    <row r="276" ht="15.75" customHeight="1">
-      <c r="A276" s="2" t="str">
+      <c r="F275" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A276" s="2">
         <f t="shared" si="1"/>
         <v>275</v>
       </c>
@@ -7943,9 +8804,12 @@
       <c r="E276" s="2" t="s">
         <v>637</v>
       </c>
-    </row>
-    <row r="277" ht="15.75" customHeight="1">
-      <c r="A277" s="2" t="str">
+      <c r="F276" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A277" s="2">
         <f t="shared" si="1"/>
         <v>276</v>
       </c>
@@ -7961,9 +8825,12 @@
       <c r="E277" s="2" t="s">
         <v>639</v>
       </c>
-    </row>
-    <row r="278" ht="15.75" customHeight="1">
-      <c r="A278" s="2" t="str">
+      <c r="F277" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A278" s="2">
         <f t="shared" si="1"/>
         <v>277</v>
       </c>
@@ -7979,9 +8846,12 @@
       <c r="E278" s="2" t="s">
         <v>641</v>
       </c>
-    </row>
-    <row r="279" ht="15.75" customHeight="1">
-      <c r="A279" s="2" t="str">
+      <c r="F278" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A279" s="2">
         <f t="shared" si="1"/>
         <v>278</v>
       </c>
@@ -7997,9 +8867,12 @@
       <c r="E279" s="2" t="s">
         <v>643</v>
       </c>
-    </row>
-    <row r="280" ht="15.75" customHeight="1">
-      <c r="A280" s="2" t="str">
+      <c r="F279" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A280" s="2">
         <f t="shared" si="1"/>
         <v>279</v>
       </c>
@@ -8015,9 +8888,12 @@
       <c r="E280" s="2" t="s">
         <v>645</v>
       </c>
-    </row>
-    <row r="281" ht="15.75" customHeight="1">
-      <c r="A281" s="2" t="str">
+      <c r="F280" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A281" s="2">
         <f t="shared" si="1"/>
         <v>280</v>
       </c>
@@ -8033,9 +8909,12 @@
       <c r="E281" s="2" t="s">
         <v>647</v>
       </c>
-    </row>
-    <row r="282" ht="15.75" customHeight="1">
-      <c r="A282" s="2" t="str">
+      <c r="F281" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A282" s="2">
         <f t="shared" si="1"/>
         <v>281</v>
       </c>
@@ -8051,9 +8930,12 @@
       <c r="E282" s="2" t="s">
         <v>650</v>
       </c>
-    </row>
-    <row r="283" ht="15.75" customHeight="1">
-      <c r="A283" s="2" t="str">
+      <c r="F282" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A283" s="2">
         <f t="shared" si="1"/>
         <v>282</v>
       </c>
@@ -8069,9 +8951,12 @@
       <c r="E283" s="2" t="s">
         <v>652</v>
       </c>
-    </row>
-    <row r="284" ht="15.75" customHeight="1">
-      <c r="A284" s="2" t="str">
+      <c r="F283" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A284" s="2">
         <f t="shared" si="1"/>
         <v>283</v>
       </c>
@@ -8087,9 +8972,12 @@
       <c r="E284" s="2" t="s">
         <v>654</v>
       </c>
-    </row>
-    <row r="285" ht="15.75" customHeight="1">
-      <c r="A285" s="2" t="str">
+      <c r="F284" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A285" s="2">
         <f t="shared" si="1"/>
         <v>284</v>
       </c>
@@ -8105,9 +8993,12 @@
       <c r="E285" s="2" t="s">
         <v>656</v>
       </c>
-    </row>
-    <row r="286" ht="15.75" customHeight="1">
-      <c r="A286" s="2" t="str">
+      <c r="F285" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A286" s="2">
         <f t="shared" si="1"/>
         <v>285</v>
       </c>
@@ -8123,9 +9014,12 @@
       <c r="E286" s="2" t="s">
         <v>658</v>
       </c>
-    </row>
-    <row r="287" ht="15.75" customHeight="1">
-      <c r="A287" s="2" t="str">
+      <c r="F286" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A287" s="2">
         <f t="shared" si="1"/>
         <v>286</v>
       </c>
@@ -8141,9 +9035,12 @@
       <c r="E287" s="2" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="288" ht="15.75" customHeight="1">
-      <c r="A288" s="2" t="str">
+      <c r="F287" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A288" s="2">
         <f t="shared" si="1"/>
         <v>287</v>
       </c>
@@ -8159,9 +9056,12 @@
       <c r="E288" s="2" t="s">
         <v>662</v>
       </c>
-    </row>
-    <row r="289" ht="15.75" customHeight="1">
-      <c r="A289" s="2" t="str">
+      <c r="F288" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A289" s="2">
         <f t="shared" si="1"/>
         <v>288</v>
       </c>
@@ -8177,9 +9077,12 @@
       <c r="E289" s="2" t="s">
         <v>664</v>
       </c>
-    </row>
-    <row r="290" ht="15.75" customHeight="1">
-      <c r="A290" s="2" t="str">
+      <c r="F289" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A290" s="2">
         <f t="shared" si="1"/>
         <v>289</v>
       </c>
@@ -8195,9 +9098,12 @@
       <c r="E290" s="2" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="291" ht="15.75" customHeight="1">
-      <c r="A291" s="2" t="str">
+      <c r="F290" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A291" s="2">
         <f t="shared" si="1"/>
         <v>290</v>
       </c>
@@ -8213,9 +9119,12 @@
       <c r="E291" s="2" t="s">
         <v>668</v>
       </c>
-    </row>
-    <row r="292" ht="15.75" customHeight="1">
-      <c r="A292" s="2" t="str">
+      <c r="F291" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A292" s="2">
         <f t="shared" si="1"/>
         <v>291</v>
       </c>
@@ -8231,9 +9140,12 @@
       <c r="E292" s="2" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="293" ht="15.75" customHeight="1">
-      <c r="A293" s="2" t="str">
+      <c r="F292" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A293" s="2">
         <f t="shared" si="1"/>
         <v>292</v>
       </c>
@@ -8249,9 +9161,12 @@
       <c r="E293" s="2" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="294" ht="15.75" customHeight="1">
-      <c r="A294" s="2" t="str">
+      <c r="F293" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A294" s="2">
         <f t="shared" si="1"/>
         <v>293</v>
       </c>
@@ -8267,9 +9182,12 @@
       <c r="E294" s="2" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="295" ht="15.75" customHeight="1">
-      <c r="A295" s="2" t="str">
+      <c r="F294" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A295" s="2">
         <f t="shared" si="1"/>
         <v>294</v>
       </c>
@@ -8285,9 +9203,12 @@
       <c r="E295" s="2" t="s">
         <v>677</v>
       </c>
-    </row>
-    <row r="296" ht="15.75" customHeight="1">
-      <c r="A296" s="2" t="str">
+      <c r="F295" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A296" s="2">
         <f t="shared" si="1"/>
         <v>295</v>
       </c>
@@ -8303,9 +9224,12 @@
       <c r="E296" s="2" t="s">
         <v>679</v>
       </c>
-    </row>
-    <row r="297" ht="15.75" customHeight="1">
-      <c r="A297" s="2" t="str">
+      <c r="F296" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A297" s="2">
         <f t="shared" si="1"/>
         <v>296</v>
       </c>
@@ -8321,9 +9245,12 @@
       <c r="E297" s="2" t="s">
         <v>681</v>
       </c>
-    </row>
-    <row r="298" ht="15.75" customHeight="1">
-      <c r="A298" s="2" t="str">
+      <c r="F297" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A298" s="2">
         <f t="shared" si="1"/>
         <v>297</v>
       </c>
@@ -8339,9 +9266,12 @@
       <c r="E298" s="2" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="299" ht="15.75" customHeight="1">
-      <c r="A299" s="2" t="str">
+      <c r="F298" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A299" s="2">
         <f t="shared" si="1"/>
         <v>298</v>
       </c>
@@ -8357,9 +9287,12 @@
       <c r="E299" s="2" t="s">
         <v>685</v>
       </c>
-    </row>
-    <row r="300" ht="15.75" customHeight="1">
-      <c r="A300" s="2" t="str">
+      <c r="F299" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A300" s="2">
         <f t="shared" si="1"/>
         <v>299</v>
       </c>
@@ -8375,9 +9308,12 @@
       <c r="E300" s="2" t="s">
         <v>687</v>
       </c>
-    </row>
-    <row r="301" ht="15.75" customHeight="1">
-      <c r="A301" s="2" t="str">
+      <c r="F300" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A301" s="2">
         <f t="shared" si="1"/>
         <v>300</v>
       </c>
@@ -8393,9 +9329,12 @@
       <c r="E301" s="2" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="302" ht="15.75" customHeight="1">
-      <c r="A302" s="2" t="str">
+      <c r="F301" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A302" s="2">
         <f t="shared" si="1"/>
         <v>301</v>
       </c>
@@ -8411,9 +9350,12 @@
       <c r="E302" s="2" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="303" ht="15.75" customHeight="1">
-      <c r="A303" s="2" t="str">
+      <c r="F302" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A303" s="2">
         <f t="shared" si="1"/>
         <v>302</v>
       </c>
@@ -8429,9 +9371,12 @@
       <c r="E303" s="2" t="s">
         <v>693</v>
       </c>
-    </row>
-    <row r="304" ht="15.75" customHeight="1">
-      <c r="A304" s="2" t="str">
+      <c r="F303" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A304" s="2">
         <f t="shared" si="1"/>
         <v>303</v>
       </c>
@@ -8447,9 +9392,12 @@
       <c r="E304" s="2" t="s">
         <v>696</v>
       </c>
-    </row>
-    <row r="305" ht="15.75" customHeight="1">
-      <c r="A305" s="2" t="str">
+      <c r="F304" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A305" s="2">
         <f t="shared" si="1"/>
         <v>304</v>
       </c>
@@ -8465,9 +9413,12 @@
       <c r="E305" s="2" t="s">
         <v>698</v>
       </c>
-    </row>
-    <row r="306" ht="15.75" customHeight="1">
-      <c r="A306" s="2" t="str">
+      <c r="F305" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A306" s="2">
         <f t="shared" si="1"/>
         <v>305</v>
       </c>
@@ -8483,9 +9434,12 @@
       <c r="E306" s="2" t="s">
         <v>700</v>
       </c>
-    </row>
-    <row r="307" ht="15.75" customHeight="1">
-      <c r="A307" s="2" t="str">
+      <c r="F306" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A307" s="2">
         <f t="shared" si="1"/>
         <v>306</v>
       </c>
@@ -8501,9 +9455,12 @@
       <c r="E307" s="2" t="s">
         <v>702</v>
       </c>
-    </row>
-    <row r="308" ht="15.75" customHeight="1">
-      <c r="A308" s="2" t="str">
+      <c r="F307" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A308" s="2">
         <f t="shared" si="1"/>
         <v>307</v>
       </c>
@@ -8519,9 +9476,12 @@
       <c r="E308" s="2" t="s">
         <v>704</v>
       </c>
-    </row>
-    <row r="309" ht="15.75" customHeight="1">
-      <c r="A309" s="2" t="str">
+      <c r="F308" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A309" s="2">
         <f t="shared" si="1"/>
         <v>308</v>
       </c>
@@ -8537,9 +9497,12 @@
       <c r="E309" s="2" t="s">
         <v>706</v>
       </c>
-    </row>
-    <row r="310" ht="15.75" customHeight="1">
-      <c r="A310" s="2" t="str">
+      <c r="F309" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A310" s="2">
         <f t="shared" si="1"/>
         <v>309</v>
       </c>
@@ -8555,9 +9518,12 @@
       <c r="E310" s="2" t="s">
         <v>708</v>
       </c>
-    </row>
-    <row r="311" ht="15.75" customHeight="1">
-      <c r="A311" s="2" t="str">
+      <c r="F310" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A311" s="2">
         <f t="shared" si="1"/>
         <v>310</v>
       </c>
@@ -8573,9 +9539,12 @@
       <c r="E311" s="2" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="312" ht="15.75" customHeight="1">
-      <c r="A312" s="2" t="str">
+      <c r="F311" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A312" s="2">
         <f t="shared" si="1"/>
         <v>311</v>
       </c>
@@ -8591,9 +9560,12 @@
       <c r="E312" s="2" t="s">
         <v>712</v>
       </c>
-    </row>
-    <row r="313" ht="15.75" customHeight="1">
-      <c r="A313" s="2" t="str">
+      <c r="F312" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A313" s="2">
         <f t="shared" si="1"/>
         <v>312</v>
       </c>
@@ -8609,9 +9581,12 @@
       <c r="E313" s="2" t="s">
         <v>714</v>
       </c>
-    </row>
-    <row r="314" ht="15.75" customHeight="1">
-      <c r="A314" s="2" t="str">
+      <c r="F313" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A314" s="2">
         <f t="shared" si="1"/>
         <v>313</v>
       </c>
@@ -8627,9 +9602,12 @@
       <c r="E314" s="2" t="s">
         <v>716</v>
       </c>
-    </row>
-    <row r="315" ht="15.75" customHeight="1">
-      <c r="A315" s="2" t="str">
+      <c r="F314" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A315" s="2">
         <f t="shared" si="1"/>
         <v>314</v>
       </c>
@@ -8645,9 +9623,12 @@
       <c r="E315" s="2" t="s">
         <v>718</v>
       </c>
-    </row>
-    <row r="316" ht="15.75" customHeight="1">
-      <c r="A316" s="2" t="str">
+      <c r="F315" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A316" s="2">
         <f t="shared" si="1"/>
         <v>315</v>
       </c>
@@ -8663,9 +9644,12 @@
       <c r="E316" s="2" t="s">
         <v>720</v>
       </c>
-    </row>
-    <row r="317" ht="15.75" customHeight="1">
-      <c r="A317" s="2" t="str">
+      <c r="F316" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A317" s="2">
         <f t="shared" si="1"/>
         <v>316</v>
       </c>
@@ -8681,9 +9665,12 @@
       <c r="E317" s="2" t="s">
         <v>722</v>
       </c>
-    </row>
-    <row r="318" ht="15.75" customHeight="1">
-      <c r="A318" s="2" t="str">
+      <c r="F317" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A318" s="2">
         <f t="shared" si="1"/>
         <v>317</v>
       </c>
@@ -8699,9 +9686,12 @@
       <c r="E318" s="2" t="s">
         <v>725</v>
       </c>
-    </row>
-    <row r="319" ht="15.75" customHeight="1">
-      <c r="A319" s="2" t="str">
+      <c r="F318" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A319" s="2">
         <f t="shared" si="1"/>
         <v>318</v>
       </c>
@@ -8717,9 +9707,12 @@
       <c r="E319" s="2" t="s">
         <v>727</v>
       </c>
-    </row>
-    <row r="320" ht="15.75" customHeight="1">
-      <c r="A320" s="2" t="str">
+      <c r="F319" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A320" s="2">
         <f t="shared" si="1"/>
         <v>319</v>
       </c>
@@ -8735,9 +9728,12 @@
       <c r="E320" s="2" t="s">
         <v>729</v>
       </c>
-    </row>
-    <row r="321" ht="15.75" customHeight="1">
-      <c r="A321" s="2" t="str">
+      <c r="F320" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A321" s="2">
         <f t="shared" si="1"/>
         <v>320</v>
       </c>
@@ -8753,9 +9749,12 @@
       <c r="E321" s="2" t="s">
         <v>731</v>
       </c>
-    </row>
-    <row r="322" ht="15.75" customHeight="1">
-      <c r="A322" s="2" t="str">
+      <c r="F321" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A322" s="2">
         <f t="shared" si="1"/>
         <v>321</v>
       </c>
@@ -8771,9 +9770,12 @@
       <c r="E322" s="2" t="s">
         <v>733</v>
       </c>
-    </row>
-    <row r="323" ht="15.75" customHeight="1">
-      <c r="A323" s="2" t="str">
+      <c r="F322" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A323" s="2">
         <f t="shared" si="1"/>
         <v>322</v>
       </c>
@@ -8789,9 +9791,12 @@
       <c r="E323" s="2" t="s">
         <v>735</v>
       </c>
-    </row>
-    <row r="324" ht="15.75" customHeight="1">
-      <c r="A324" s="2" t="str">
+      <c r="F323" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A324" s="2">
         <f t="shared" si="1"/>
         <v>323</v>
       </c>
@@ -8807,9 +9812,12 @@
       <c r="E324" s="2" t="s">
         <v>737</v>
       </c>
-    </row>
-    <row r="325" ht="15.75" customHeight="1">
-      <c r="A325" s="2" t="str">
+      <c r="F324" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A325" s="2">
         <f t="shared" si="1"/>
         <v>324</v>
       </c>
@@ -8825,9 +9833,12 @@
       <c r="E325" s="2" t="s">
         <v>741</v>
       </c>
-    </row>
-    <row r="326" ht="15.75" customHeight="1">
-      <c r="A326" s="2" t="str">
+      <c r="F325" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A326" s="2">
         <f t="shared" si="1"/>
         <v>325</v>
       </c>
@@ -8843,9 +9854,12 @@
       <c r="E326" s="2" t="s">
         <v>743</v>
       </c>
-    </row>
-    <row r="327" ht="15.75" customHeight="1">
-      <c r="A327" s="2" t="str">
+      <c r="F326" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A327" s="2">
         <f t="shared" si="1"/>
         <v>326</v>
       </c>
@@ -8861,9 +9875,12 @@
       <c r="E327" s="2" t="s">
         <v>745</v>
       </c>
-    </row>
-    <row r="328" ht="15.75" customHeight="1">
-      <c r="A328" s="2" t="str">
+      <c r="F327" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A328" s="2">
         <f t="shared" si="1"/>
         <v>327</v>
       </c>
@@ -8879,9 +9896,12 @@
       <c r="E328" s="2" t="s">
         <v>747</v>
       </c>
-    </row>
-    <row r="329" ht="15.75" customHeight="1">
-      <c r="A329" s="2" t="str">
+      <c r="F328" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A329" s="2">
         <f t="shared" si="1"/>
         <v>328</v>
       </c>
@@ -8897,9 +9917,12 @@
       <c r="E329" s="2" t="s">
         <v>749</v>
       </c>
-    </row>
-    <row r="330" ht="15.75" customHeight="1">
-      <c r="A330" s="2" t="str">
+      <c r="F329" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A330" s="2">
         <f t="shared" si="1"/>
         <v>329</v>
       </c>
@@ -8915,9 +9938,12 @@
       <c r="E330" s="2" t="s">
         <v>751</v>
       </c>
-    </row>
-    <row r="331" ht="15.75" customHeight="1">
-      <c r="A331" s="2" t="str">
+      <c r="F330" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A331" s="2">
         <f t="shared" si="1"/>
         <v>330</v>
       </c>
@@ -8933,9 +9959,12 @@
       <c r="E331" s="2" t="s">
         <v>753</v>
       </c>
-    </row>
-    <row r="332" ht="15.75" customHeight="1">
-      <c r="A332" s="2" t="str">
+      <c r="F331" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A332" s="2">
         <f t="shared" si="1"/>
         <v>331</v>
       </c>
@@ -8951,9 +9980,12 @@
       <c r="E332" s="2" t="s">
         <v>755</v>
       </c>
-    </row>
-    <row r="333" ht="15.75" customHeight="1">
-      <c r="A333" s="2" t="str">
+      <c r="F332" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A333" s="2">
         <f t="shared" si="1"/>
         <v>332</v>
       </c>
@@ -8969,9 +10001,12 @@
       <c r="E333" s="2" t="s">
         <v>758</v>
       </c>
-    </row>
-    <row r="334" ht="15.75" customHeight="1">
-      <c r="A334" s="2" t="str">
+      <c r="F333" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A334" s="2">
         <f t="shared" si="1"/>
         <v>333</v>
       </c>
@@ -8987,9 +10022,12 @@
       <c r="E334" s="2" t="s">
         <v>761</v>
       </c>
-    </row>
-    <row r="335" ht="15.75" customHeight="1">
-      <c r="A335" s="2" t="str">
+      <c r="F334" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A335" s="2">
         <f t="shared" si="1"/>
         <v>334</v>
       </c>
@@ -9005,9 +10043,12 @@
       <c r="E335" s="2" t="s">
         <v>763</v>
       </c>
-    </row>
-    <row r="336" ht="15.75" customHeight="1">
-      <c r="A336" s="2" t="str">
+      <c r="F335" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A336" s="2">
         <f t="shared" si="1"/>
         <v>335</v>
       </c>
@@ -9023,9 +10064,12 @@
       <c r="E336" s="2" t="s">
         <v>765</v>
       </c>
-    </row>
-    <row r="337" ht="15.75" customHeight="1">
-      <c r="A337" s="2" t="str">
+      <c r="F336" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A337" s="2">
         <f t="shared" si="1"/>
         <v>336</v>
       </c>
@@ -9041,9 +10085,12 @@
       <c r="E337" s="2" t="s">
         <v>767</v>
       </c>
-    </row>
-    <row r="338" ht="15.75" customHeight="1">
-      <c r="A338" s="2" t="str">
+      <c r="F337" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A338" s="2">
         <f t="shared" si="1"/>
         <v>337</v>
       </c>
@@ -9059,9 +10106,12 @@
       <c r="E338" s="2" t="s">
         <v>769</v>
       </c>
-    </row>
-    <row r="339" ht="15.75" customHeight="1">
-      <c r="A339" s="2" t="str">
+      <c r="F338" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A339" s="2">
         <f t="shared" si="1"/>
         <v>338</v>
       </c>
@@ -9077,9 +10127,12 @@
       <c r="E339" s="2" t="s">
         <v>771</v>
       </c>
-    </row>
-    <row r="340" ht="15.75" customHeight="1">
-      <c r="A340" s="2" t="str">
+      <c r="F339" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A340" s="2">
         <f t="shared" si="1"/>
         <v>339</v>
       </c>
@@ -9095,9 +10148,12 @@
       <c r="E340" s="2" t="s">
         <v>773</v>
       </c>
-    </row>
-    <row r="341" ht="15.75" customHeight="1">
-      <c r="A341" s="2" t="str">
+      <c r="F340" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A341" s="2">
         <f t="shared" si="1"/>
         <v>340</v>
       </c>
@@ -9113,9 +10169,12 @@
       <c r="E341" s="2" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="342" ht="15.75" customHeight="1">
-      <c r="A342" s="2" t="str">
+      <c r="F341" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A342" s="2">
         <f t="shared" si="1"/>
         <v>341</v>
       </c>
@@ -9131,9 +10190,12 @@
       <c r="E342" s="2" t="s">
         <v>777</v>
       </c>
-    </row>
-    <row r="343" ht="15.75" customHeight="1">
-      <c r="A343" s="2" t="str">
+      <c r="F342" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A343" s="2">
         <f t="shared" si="1"/>
         <v>342</v>
       </c>
@@ -9149,9 +10211,12 @@
       <c r="E343" s="2" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="344" ht="15.75" customHeight="1">
-      <c r="A344" s="2" t="str">
+      <c r="F343" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A344" s="2">
         <f t="shared" si="1"/>
         <v>343</v>
       </c>
@@ -9167,9 +10232,12 @@
       <c r="E344" s="2" t="s">
         <v>781</v>
       </c>
-    </row>
-    <row r="345" ht="15.75" customHeight="1">
-      <c r="A345" s="2" t="str">
+      <c r="F344" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A345" s="2">
         <f t="shared" si="1"/>
         <v>344</v>
       </c>
@@ -9185,9 +10253,12 @@
       <c r="E345" s="2" t="s">
         <v>783</v>
       </c>
-    </row>
-    <row r="346" ht="15.75" customHeight="1">
-      <c r="A346" s="2" t="str">
+      <c r="F345" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A346" s="2">
         <f t="shared" si="1"/>
         <v>345</v>
       </c>
@@ -9203,9 +10274,12 @@
       <c r="E346" s="2" t="s">
         <v>785</v>
       </c>
-    </row>
-    <row r="347" ht="15.75" customHeight="1">
-      <c r="A347" s="2" t="str">
+      <c r="F346" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A347" s="2">
         <f t="shared" si="1"/>
         <v>346</v>
       </c>
@@ -9221,9 +10295,12 @@
       <c r="E347" s="2" t="s">
         <v>787</v>
       </c>
-    </row>
-    <row r="348" ht="15.75" customHeight="1">
-      <c r="A348" s="2" t="str">
+      <c r="F347" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A348" s="2">
         <f t="shared" si="1"/>
         <v>347</v>
       </c>
@@ -9239,9 +10316,12 @@
       <c r="E348" s="2" t="s">
         <v>789</v>
       </c>
-    </row>
-    <row r="349" ht="15.75" customHeight="1">
-      <c r="A349" s="2" t="str">
+      <c r="F348" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A349" s="2">
         <f t="shared" si="1"/>
         <v>348</v>
       </c>
@@ -9257,9 +10337,12 @@
       <c r="E349" s="2" t="s">
         <v>791</v>
       </c>
-    </row>
-    <row r="350" ht="15.75" customHeight="1">
-      <c r="A350" s="2" t="str">
+      <c r="F349" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A350" s="2">
         <f t="shared" si="1"/>
         <v>349</v>
       </c>
@@ -9275,9 +10358,12 @@
       <c r="E350" s="2" t="s">
         <v>793</v>
       </c>
-    </row>
-    <row r="351" ht="15.75" customHeight="1">
-      <c r="A351" s="2" t="str">
+      <c r="F350" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A351" s="2">
         <f t="shared" si="1"/>
         <v>350</v>
       </c>
@@ -9293,9 +10379,12 @@
       <c r="E351" s="2" t="s">
         <v>795</v>
       </c>
-    </row>
-    <row r="352" ht="15.75" customHeight="1">
-      <c r="A352" s="2" t="str">
+      <c r="F351" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A352" s="2">
         <f t="shared" si="1"/>
         <v>351</v>
       </c>
@@ -9311,9 +10400,12 @@
       <c r="E352" s="2" t="s">
         <v>797</v>
       </c>
-    </row>
-    <row r="353" ht="15.75" customHeight="1">
-      <c r="A353" s="2" t="str">
+      <c r="F352" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A353" s="2">
         <f t="shared" si="1"/>
         <v>352</v>
       </c>
@@ -9329,9 +10421,12 @@
       <c r="E353" s="2" t="s">
         <v>799</v>
       </c>
-    </row>
-    <row r="354" ht="15.75" customHeight="1">
-      <c r="A354" s="2" t="str">
+      <c r="F353" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A354" s="2">
         <f t="shared" si="1"/>
         <v>353</v>
       </c>
@@ -9347,9 +10442,12 @@
       <c r="E354" s="2" t="s">
         <v>801</v>
       </c>
-    </row>
-    <row r="355" ht="15.75" customHeight="1">
-      <c r="A355" s="2" t="str">
+      <c r="F354" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A355" s="2">
         <f t="shared" si="1"/>
         <v>354</v>
       </c>
@@ -9365,9 +10463,12 @@
       <c r="E355" s="2" t="s">
         <v>803</v>
       </c>
-    </row>
-    <row r="356" ht="15.75" customHeight="1">
-      <c r="A356" s="2" t="str">
+      <c r="F355" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A356" s="2">
         <f t="shared" si="1"/>
         <v>355</v>
       </c>
@@ -9383,9 +10484,12 @@
       <c r="E356" s="2" t="s">
         <v>805</v>
       </c>
-    </row>
-    <row r="357" ht="15.75" customHeight="1">
-      <c r="A357" s="2" t="str">
+      <c r="F356" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A357" s="2">
         <f t="shared" si="1"/>
         <v>356</v>
       </c>
@@ -9401,9 +10505,12 @@
       <c r="E357" s="2" t="s">
         <v>807</v>
       </c>
-    </row>
-    <row r="358" ht="15.75" customHeight="1">
-      <c r="A358" s="2" t="str">
+      <c r="F357" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A358" s="2">
         <f t="shared" si="1"/>
         <v>357</v>
       </c>
@@ -9419,9 +10526,12 @@
       <c r="E358" s="2" t="s">
         <v>809</v>
       </c>
-    </row>
-    <row r="359" ht="15.75" customHeight="1">
-      <c r="A359" s="2" t="str">
+      <c r="F358" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A359" s="2">
         <f t="shared" si="1"/>
         <v>358</v>
       </c>
@@ -9437,9 +10547,12 @@
       <c r="E359" s="2" t="s">
         <v>811</v>
       </c>
-    </row>
-    <row r="360" ht="15.75" customHeight="1">
-      <c r="A360" s="2" t="str">
+      <c r="F359" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A360" s="2">
         <f t="shared" si="1"/>
         <v>359</v>
       </c>
@@ -9455,9 +10568,12 @@
       <c r="E360" s="2" t="s">
         <v>813</v>
       </c>
-    </row>
-    <row r="361" ht="15.75" customHeight="1">
-      <c r="A361" s="2" t="str">
+      <c r="F360" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A361" s="2">
         <f t="shared" si="1"/>
         <v>360</v>
       </c>
@@ -9473,9 +10589,12 @@
       <c r="E361" s="2" t="s">
         <v>815</v>
       </c>
-    </row>
-    <row r="362" ht="15.75" customHeight="1">
-      <c r="A362" s="2" t="str">
+      <c r="F361" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A362" s="2">
         <f t="shared" si="1"/>
         <v>361</v>
       </c>
@@ -9491,9 +10610,12 @@
       <c r="E362" s="2" t="s">
         <v>817</v>
       </c>
-    </row>
-    <row r="363" ht="15.75" customHeight="1">
-      <c r="A363" s="2" t="str">
+      <c r="F362" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A363" s="2">
         <f t="shared" si="1"/>
         <v>362</v>
       </c>
@@ -9509,9 +10631,12 @@
       <c r="E363" s="2" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="364" ht="15.75" customHeight="1">
-      <c r="A364" s="2" t="str">
+      <c r="F363" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A364" s="2">
         <f t="shared" si="1"/>
         <v>363</v>
       </c>
@@ -9527,9 +10652,12 @@
       <c r="E364" s="2" t="s">
         <v>821</v>
       </c>
-    </row>
-    <row r="365" ht="15.75" customHeight="1">
-      <c r="A365" s="2" t="str">
+      <c r="F364" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A365" s="2">
         <f t="shared" si="1"/>
         <v>364</v>
       </c>
@@ -9545,9 +10673,12 @@
       <c r="E365" s="2" t="s">
         <v>823</v>
       </c>
-    </row>
-    <row r="366" ht="15.75" customHeight="1">
-      <c r="A366" s="2" t="str">
+      <c r="F365" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A366" s="2">
         <f t="shared" si="1"/>
         <v>365</v>
       </c>
@@ -9563,9 +10694,12 @@
       <c r="E366" s="2" t="s">
         <v>825</v>
       </c>
-    </row>
-    <row r="367" ht="15.75" customHeight="1">
-      <c r="A367" s="2" t="str">
+      <c r="F366" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A367" s="2">
         <f t="shared" si="1"/>
         <v>366</v>
       </c>
@@ -9581,9 +10715,12 @@
       <c r="E367" s="2" t="s">
         <v>828</v>
       </c>
-    </row>
-    <row r="368" ht="15.75" customHeight="1">
-      <c r="A368" s="2" t="str">
+      <c r="F367" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A368" s="2">
         <f t="shared" si="1"/>
         <v>367</v>
       </c>
@@ -9599,9 +10736,12 @@
       <c r="E368" s="2" t="s">
         <v>830</v>
       </c>
-    </row>
-    <row r="369" ht="15.75" customHeight="1">
-      <c r="A369" s="2" t="str">
+      <c r="F368" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A369" s="2">
         <f t="shared" si="1"/>
         <v>368</v>
       </c>
@@ -9617,9 +10757,12 @@
       <c r="E369" s="2" t="s">
         <v>832</v>
       </c>
-    </row>
-    <row r="370" ht="15.75" customHeight="1">
-      <c r="A370" s="2" t="str">
+      <c r="F369" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A370" s="2">
         <f t="shared" si="1"/>
         <v>369</v>
       </c>
@@ -9635,9 +10778,12 @@
       <c r="E370" s="2" t="s">
         <v>834</v>
       </c>
-    </row>
-    <row r="371" ht="15.75" customHeight="1">
-      <c r="A371" s="2" t="str">
+      <c r="F370" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A371" s="2">
         <f t="shared" si="1"/>
         <v>370</v>
       </c>
@@ -9653,9 +10799,12 @@
       <c r="E371" s="2" t="s">
         <v>836</v>
       </c>
-    </row>
-    <row r="372" ht="15.75" customHeight="1">
-      <c r="A372" s="2" t="str">
+      <c r="F371" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A372" s="2">
         <f t="shared" si="1"/>
         <v>371</v>
       </c>
@@ -9671,9 +10820,12 @@
       <c r="E372" s="2" t="s">
         <v>838</v>
       </c>
-    </row>
-    <row r="373" ht="15.75" customHeight="1">
-      <c r="A373" s="2" t="str">
+      <c r="F372" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A373" s="2">
         <f t="shared" si="1"/>
         <v>372</v>
       </c>
@@ -9689,9 +10841,12 @@
       <c r="E373" s="2" t="s">
         <v>840</v>
       </c>
-    </row>
-    <row r="374" ht="15.75" customHeight="1">
-      <c r="A374" s="2" t="str">
+      <c r="F373" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A374" s="2">
         <f t="shared" si="1"/>
         <v>373</v>
       </c>
@@ -9707,9 +10862,12 @@
       <c r="E374" s="2" t="s">
         <v>842</v>
       </c>
-    </row>
-    <row r="375" ht="15.75" customHeight="1">
-      <c r="A375" s="2" t="str">
+      <c r="F374" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A375" s="2">
         <f t="shared" si="1"/>
         <v>374</v>
       </c>
@@ -9725,9 +10883,12 @@
       <c r="E375" s="2" t="s">
         <v>844</v>
       </c>
-    </row>
-    <row r="376" ht="15.75" customHeight="1">
-      <c r="A376" s="2" t="str">
+      <c r="F375" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A376" s="2">
         <f t="shared" si="1"/>
         <v>375</v>
       </c>
@@ -9743,9 +10904,12 @@
       <c r="E376" s="2" t="s">
         <v>846</v>
       </c>
-    </row>
-    <row r="377" ht="15.75" customHeight="1">
-      <c r="A377" s="2" t="str">
+      <c r="F376" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A377" s="2">
         <f t="shared" si="1"/>
         <v>376</v>
       </c>
@@ -9761,9 +10925,12 @@
       <c r="E377" s="2" t="s">
         <v>848</v>
       </c>
-    </row>
-    <row r="378" ht="15.75" customHeight="1">
-      <c r="A378" s="2" t="str">
+      <c r="F377" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A378" s="2">
         <f t="shared" si="1"/>
         <v>377</v>
       </c>
@@ -9779,9 +10946,12 @@
       <c r="E378" s="2" t="s">
         <v>852</v>
       </c>
-    </row>
-    <row r="379" ht="15.75" customHeight="1">
-      <c r="A379" s="2" t="str">
+      <c r="F378" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A379" s="2">
         <f t="shared" si="1"/>
         <v>378</v>
       </c>
@@ -9797,9 +10967,12 @@
       <c r="E379" s="2" t="s">
         <v>854</v>
       </c>
-    </row>
-    <row r="380" ht="15.75" customHeight="1">
-      <c r="A380" s="2" t="str">
+      <c r="F379" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A380" s="2">
         <f t="shared" si="1"/>
         <v>379</v>
       </c>
@@ -9815,12 +10988,40 @@
       <c r="E380" s="2" t="s">
         <v>858</v>
       </c>
+      <c r="F380" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A381" s="2">
+        <f t="shared" si="1"/>
+        <v>380</v>
+      </c>
+      <c r="B381" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="C381" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="D381" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="E381" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="F381" s="2" t="s">
+        <v>865</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$E$380"/>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <autoFilter ref="A1:F381" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="Used"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/database.xlsx
+++ b/database.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\Semester 7\Laporan\KP - Rival\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\Semester 7\Laporan\KP - Rival\Project KP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C175351-0423-4D9E-A7E6-1385821076EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{761D1A87-B447-493E-95C0-79E546808C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3000,7 +3000,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:F381"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3033,7 +3032,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <f t="shared" ref="A2:A256" si="0">ROW(A1)</f>
         <v>1</v>
@@ -3117,7 +3116,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -3138,7 +3137,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -3159,7 +3158,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -3201,7 +3200,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -3222,7 +3221,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -3243,7 +3242,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -3369,7 +3368,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -3453,7 +3452,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -3474,7 +3473,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -3495,7 +3494,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -3516,7 +3515,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -3537,7 +3536,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -3558,7 +3557,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -3579,7 +3578,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -3600,7 +3599,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -3621,7 +3620,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -3642,7 +3641,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -3768,7 +3767,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -3789,7 +3788,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -3810,7 +3809,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -4188,7 +4187,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -4209,7 +4208,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -4230,7 +4229,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -4251,7 +4250,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -4272,7 +4271,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -4293,7 +4292,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <f t="shared" si="0"/>
         <v>61</v>
@@ -4671,7 +4670,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <f t="shared" si="0"/>
         <v>79</v>
@@ -4860,7 +4859,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <f t="shared" si="0"/>
         <v>88</v>
@@ -4881,7 +4880,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <f t="shared" si="0"/>
         <v>89</v>
@@ -4902,7 +4901,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <f t="shared" si="0"/>
         <v>90</v>
@@ -4923,7 +4922,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <f t="shared" si="0"/>
         <v>91</v>
@@ -4944,7 +4943,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <f t="shared" si="0"/>
         <v>92</v>
@@ -4965,7 +4964,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <f t="shared" si="0"/>
         <v>93</v>
@@ -4986,7 +4985,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <f t="shared" si="0"/>
         <v>94</v>
@@ -5007,7 +5006,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <f t="shared" si="0"/>
         <v>95</v>
@@ -5028,7 +5027,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <f t="shared" si="0"/>
         <v>96</v>
@@ -5595,7 +5594,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <f t="shared" si="0"/>
         <v>123</v>
@@ -6288,7 +6287,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="157" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
         <f t="shared" si="0"/>
         <v>156</v>
@@ -6309,7 +6308,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
         <f t="shared" si="0"/>
         <v>157</v>
@@ -6330,7 +6329,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="159" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
         <f t="shared" si="0"/>
         <v>158</v>
@@ -6351,7 +6350,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="160" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
         <f t="shared" si="0"/>
         <v>159</v>
@@ -7779,7 +7778,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="228" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2">
         <f t="shared" si="0"/>
         <v>227</v>
@@ -7968,7 +7967,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="237" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2">
         <f t="shared" si="0"/>
         <v>236</v>
@@ -7989,7 +7988,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="238" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2">
         <f t="shared" si="0"/>
         <v>237</v>
@@ -8073,7 +8072,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="242" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2">
         <f t="shared" si="0"/>
         <v>241</v>
@@ -8094,7 +8093,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="243" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2">
         <f t="shared" si="0"/>
         <v>242</v>
@@ -8115,7 +8114,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="244" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2">
         <f t="shared" si="0"/>
         <v>243</v>
@@ -8199,7 +8198,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="248" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2">
         <f t="shared" si="0"/>
         <v>247</v>
@@ -8220,7 +8219,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="249" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2">
         <f t="shared" si="0"/>
         <v>248</v>
@@ -8598,7 +8597,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="267" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2">
         <f t="shared" si="1"/>
         <v>266</v>
@@ -8619,7 +8618,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="268" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2">
         <f t="shared" si="1"/>
         <v>267</v>
@@ -8640,7 +8639,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="269" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2">
         <f t="shared" si="1"/>
         <v>268</v>
@@ -8871,7 +8870,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="280" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2">
         <f t="shared" si="1"/>
         <v>279</v>
@@ -10509,7 +10508,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="358" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="2">
         <f t="shared" si="1"/>
         <v>357</v>
@@ -10950,7 +10949,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="379" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="2">
         <f t="shared" si="1"/>
         <v>378</v>
@@ -10971,7 +10970,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="380" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="2">
         <f t="shared" si="1"/>
         <v>379</v>
@@ -10992,7 +10991,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="381" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="2">
         <f t="shared" si="1"/>
         <v>380</v>
@@ -11014,13 +11013,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F381" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="Used"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:F381" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
